--- a/posiciones_buscador.xlsx
+++ b/posiciones_buscador.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SYSTEMAS\Desktop\GPO CANAVE\Buscador de posiciones\BUSCADOR VERSION WEB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\desarrollos\buscador_posiciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1AA9DAC-876F-48C7-B980-1E037914192A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC77DC0F-C466-4BCF-B0F5-B973C351A5F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{81345FCE-0991-44B1-AB97-4BC767A118BC}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81345FCE-0991-44B1-AB97-4BC767A118BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Productos_posicion (2)" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4842" uniqueCount="1537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4877" uniqueCount="1544">
   <si>
     <t>Cod. De Barras</t>
   </si>
@@ -4650,6 +4650,27 @@
   </si>
   <si>
     <t>TOALLITAS HUMEDAS  A BEAUTILFUL DAY</t>
+  </si>
+  <si>
+    <t>VINAGRE DE MANZANA CON MIEL DE ABEJA</t>
+  </si>
+  <si>
+    <t>VINAGRE DE SIDRA DE MANZANA</t>
+  </si>
+  <si>
+    <t>PROMEGA 3</t>
+  </si>
+  <si>
+    <t>MELATONINA 5 MG C/30</t>
+  </si>
+  <si>
+    <t>ZINC C/60</t>
+  </si>
+  <si>
+    <t>OMEGA 3 EPA/DHA C/ 30</t>
+  </si>
+  <si>
+    <t>OMEGA 3,6,9, EPA/DHA CON ACEITE DE LINAZA Y OLIVO C/30</t>
   </si>
 </sst>
 </file>
@@ -4684,15 +4705,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -4724,11 +4751,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
@@ -4753,6 +4800,19 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4848,8 +4908,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G968" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G968" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G975" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G975" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G967">
     <sortCondition ref="C1:C967"/>
   </sortState>
@@ -5185,7 +5245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD76C0E-5FFA-48DF-BC8E-37CFF7587C46}">
-  <dimension ref="A1:G968"/>
+  <dimension ref="A1:G975"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
@@ -27457,10 +27517,172 @@
         <v>10</v>
       </c>
     </row>
+    <row r="969" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A969" s="18">
+        <v>7505023010867</v>
+      </c>
+      <c r="B969" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C969" s="14">
+        <v>9990</v>
+      </c>
+      <c r="D969" s="16" t="s">
+        <v>1537</v>
+      </c>
+      <c r="E969" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F969" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G969" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="970" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A970" s="19">
+        <v>7505023011239</v>
+      </c>
+      <c r="B970" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C970" s="15">
+        <v>9991</v>
+      </c>
+      <c r="D970" s="16" t="s">
+        <v>1538</v>
+      </c>
+      <c r="E970" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F970" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G970" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="971" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A971" s="20">
+        <v>7503008344501</v>
+      </c>
+      <c r="B971" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C971" s="16">
+        <v>9794</v>
+      </c>
+      <c r="D971" s="16" t="s">
+        <v>1539</v>
+      </c>
+      <c r="E971" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F971" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G971" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="972" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A972" s="21">
+        <v>7505023010928</v>
+      </c>
+      <c r="B972" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C972" s="17">
+        <v>9992</v>
+      </c>
+      <c r="D972" s="16" t="s">
+        <v>1540</v>
+      </c>
+      <c r="E972" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F972" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G972" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="973" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A973" s="21">
+        <v>7502324110623</v>
+      </c>
+      <c r="B973" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C973" s="17">
+        <v>9993</v>
+      </c>
+      <c r="D973" s="16" t="s">
+        <v>1541</v>
+      </c>
+      <c r="E973" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F973" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G973" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="974" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A974" s="20">
+        <v>7506577801185</v>
+      </c>
+      <c r="B974" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C974" s="16">
+        <v>9994</v>
+      </c>
+      <c r="D974" s="16" t="s">
+        <v>1542</v>
+      </c>
+      <c r="E974" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F974" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G974" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="975" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A975" s="20">
+        <v>7506577801178</v>
+      </c>
+      <c r="B975" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C975" s="22">
+        <v>9995</v>
+      </c>
+      <c r="D975" s="16" t="s">
+        <v>1543</v>
+      </c>
+      <c r="E975" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F975" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G975" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="D2:D967" calculatedColumn="1"/>
+    <ignoredError sqref="D2:D969 D970:D975" calculatedColumn="1"/>
+    <ignoredError sqref="B949:B950" numberStoredAsText="1"/>
   </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/posiciones_buscador.xlsx
+++ b/posiciones_buscador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\desarrollos\buscador_posiciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC77DC0F-C466-4BCF-B0F5-B973C351A5F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F1209B-6E85-4A5F-9DBB-B9E7607CFE66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81345FCE-0991-44B1-AB97-4BC767A118BC}"/>
   </bookViews>
@@ -4193,9 +4193,6 @@
     <t>7501493889545</t>
   </si>
   <si>
-    <t>7503003406242, 7506346600308, 75968431605</t>
-  </si>
-  <si>
     <t>780083140205</t>
   </si>
   <si>
@@ -4671,6 +4668,9 @@
   </si>
   <si>
     <t>OMEGA 3,6,9, EPA/DHA CON ACEITE DE LINAZA Y OLIVO C/30</t>
+  </si>
+  <si>
+    <t>7503003406242, 7506346600308, 75968431605, 6650376816114</t>
   </si>
 </sst>
 </file>
@@ -16206,7 +16206,7 @@
         <v>7503003406242</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>1384</v>
+        <v>1543</v>
       </c>
       <c r="C477" s="2">
         <v>683</v>
@@ -16275,7 +16275,7 @@
         <v>780083139759</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="C480" s="2">
         <v>687</v>
@@ -16298,7 +16298,7 @@
         <v>780083140212</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="C481" s="2">
         <v>688</v>
@@ -16321,7 +16321,7 @@
         <v>7502009746215</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="C482" s="2">
         <v>690</v>
@@ -16344,7 +16344,7 @@
         <v>7501349020962</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="C483" s="2">
         <v>692</v>
@@ -16367,7 +16367,7 @@
         <v>656599041216</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="C484" s="2">
         <v>693</v>
@@ -16390,7 +16390,7 @@
         <v>785118753788</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="C485" s="2">
         <v>694</v>
@@ -16459,7 +16459,7 @@
         <v>7503000422283</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="C488" s="2">
         <v>698</v>
@@ -16482,7 +16482,7 @@
         <v>7501075715095</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="C489" s="2">
         <v>699</v>
@@ -16505,7 +16505,7 @@
         <v>7501075715088</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="C490" s="2">
         <v>700</v>
@@ -16528,7 +16528,7 @@
         <v>7501547522145</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="C491" s="2">
         <v>701</v>
@@ -16574,7 +16574,7 @@
         <v>750200165441</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="C493" s="2">
         <v>704</v>
@@ -16597,7 +16597,7 @@
         <v>7501471888249</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C494" s="2">
         <v>709</v>
@@ -16620,7 +16620,7 @@
         <v>7501258205078</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="C495" s="2">
         <v>710</v>
@@ -16643,7 +16643,7 @@
         <v>7502216798786</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="C496" s="2">
         <v>711</v>
@@ -16666,7 +16666,7 @@
         <v>7502211782483</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="C497" s="2">
         <v>712</v>
@@ -16689,7 +16689,7 @@
         <v>780083148423</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="C498" s="2">
         <v>713</v>
@@ -16735,7 +16735,7 @@
         <v>7502009744983</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="C500" s="2">
         <v>716</v>
@@ -16758,7 +16758,7 @@
         <v>780083143565</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="C501" s="2">
         <v>717</v>
@@ -16781,7 +16781,7 @@
         <v>7501075717686</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="C502" s="2">
         <v>718</v>
@@ -16804,7 +16804,7 @@
         <v>7501349029170</v>
       </c>
       <c r="B503" s="1" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="C503" s="2">
         <v>719</v>
@@ -16827,7 +16827,7 @@
         <v>7502216808614</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="C504" s="2">
         <v>720</v>
@@ -16850,7 +16850,7 @@
         <v>7502216808645</v>
       </c>
       <c r="B505" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="C505" s="2">
         <v>721</v>
@@ -16873,7 +16873,7 @@
         <v>75049812</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C506" s="2">
         <v>722</v>
@@ -16896,7 +16896,7 @@
         <v>7506022304452</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="C507" s="2">
         <v>723</v>
@@ -16942,7 +16942,7 @@
         <v>729513107890</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C509" s="2">
         <v>727</v>
@@ -16965,7 +16965,7 @@
         <v>729513107944</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="C510" s="2">
         <v>728</v>
@@ -16988,7 +16988,7 @@
         <v>780083140731</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C511" s="2">
         <v>729</v>
@@ -17011,7 +17011,7 @@
         <v>7501471889352</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="C512" s="2">
         <v>730</v>
@@ -17034,7 +17034,7 @@
         <v>729513107906</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="C513" s="2">
         <v>731</v>
@@ -17080,7 +17080,7 @@
         <v>7501289512633</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="C515" s="2">
         <v>733</v>
@@ -17103,7 +17103,7 @@
         <v>7502004530079</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="C516" s="2">
         <v>734</v>
@@ -17126,7 +17126,7 @@
         <v>729513107883</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="C517" s="2">
         <v>735</v>
@@ -17149,7 +17149,7 @@
         <v>7503002773161</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="C518" s="2">
         <v>737</v>
@@ -17172,7 +17172,7 @@
         <v>7501258206525</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="C519" s="2">
         <v>739</v>
@@ -17195,7 +17195,7 @@
         <v>7501361111501</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="C520" s="2">
         <v>740</v>
@@ -17218,7 +17218,7 @@
         <v>7502216803916</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="C521" s="2">
         <v>742</v>
@@ -17241,7 +17241,7 @@
         <v>7702136645003</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="C522" s="2">
         <v>744</v>
@@ -17264,7 +17264,7 @@
         <v>736211494979</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="C523" s="2">
         <v>746</v>
@@ -17287,7 +17287,7 @@
         <v>785120754841</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="C524" s="2">
         <v>747</v>
@@ -17310,7 +17310,7 @@
         <v>785120755046</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="C525" s="2">
         <v>748</v>
@@ -17333,7 +17333,7 @@
         <v>785120755022</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="C526" s="2">
         <v>749</v>
@@ -17356,7 +17356,7 @@
         <v>7501349025806</v>
       </c>
       <c r="B527" s="1" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="C527" s="2">
         <v>751</v>
@@ -17379,7 +17379,7 @@
         <v>7501493888784</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="C528" s="2">
         <v>752</v>
@@ -17402,7 +17402,7 @@
         <v>7502216797369</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C529" s="2">
         <v>753</v>
@@ -17448,7 +17448,7 @@
         <v>637420200897</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C531" s="2">
         <v>758</v>
@@ -17471,7 +17471,7 @@
         <v>7501250882024</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="C532" s="2">
         <v>759</v>
@@ -17494,7 +17494,7 @@
         <v>7502009743986</v>
       </c>
       <c r="B533" s="1" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="C533" s="2">
         <v>766</v>
@@ -17517,7 +17517,7 @@
         <v>7502009747168</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="C534" s="2">
         <v>767</v>
@@ -17747,7 +17747,7 @@
         <v>729513100686</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="C544" s="2">
         <v>780</v>
@@ -17793,7 +17793,7 @@
         <v>759684155017</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="C546" s="2">
         <v>782</v>
@@ -17839,7 +17839,7 @@
         <v>759684351051</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="C548" s="2">
         <v>789</v>
@@ -17862,7 +17862,7 @@
         <v>7503003406402</v>
       </c>
       <c r="B549" s="1" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="C549" s="2">
         <v>794</v>
@@ -17885,7 +17885,7 @@
         <v>759684432071</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="C550" s="2">
         <v>795</v>
@@ -17908,7 +17908,7 @@
         <v>780083148843</v>
       </c>
       <c r="B551" s="1" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="C551" s="2">
         <v>800</v>
@@ -17931,7 +17931,7 @@
         <v>780083146955</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="C552" s="2">
         <v>803</v>
@@ -17954,7 +17954,7 @@
         <v>7501825305149</v>
       </c>
       <c r="B553" s="1" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="C553" s="2">
         <v>804</v>
@@ -17977,7 +17977,7 @@
         <v>7502009747373</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="C554" s="2">
         <v>811</v>
@@ -18046,7 +18046,7 @@
         <v>7502003389975</v>
       </c>
       <c r="B557" s="1" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="C557" s="2">
         <v>826</v>
@@ -18115,7 +18115,7 @@
         <v>7502268542207</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="C560" s="2">
         <v>831</v>
@@ -18161,7 +18161,7 @@
         <v>7502247373914</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="C562" s="2">
         <v>835</v>
@@ -18437,7 +18437,7 @@
         <v>759684900105</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C574" s="2">
         <v>874</v>
@@ -18460,7 +18460,7 @@
         <v>759684311451</v>
       </c>
       <c r="B575" s="1" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="C575" s="2">
         <v>875</v>
@@ -18506,7 +18506,7 @@
         <v>7501590286223</v>
       </c>
       <c r="B577" s="1" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="C577" s="2">
         <v>878</v>
@@ -18552,7 +18552,7 @@
         <v>7501590284779</v>
       </c>
       <c r="B579" s="1" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="C579" s="2">
         <v>881</v>
@@ -18621,7 +18621,7 @@
         <v>773042188775</v>
       </c>
       <c r="B582" s="1" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="C582" s="2">
         <v>884</v>
@@ -18759,7 +18759,7 @@
         <v>0</v>
       </c>
       <c r="B588" s="1" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="C588" s="2">
         <v>893</v>
@@ -18782,7 +18782,7 @@
         <v>759684154034</v>
       </c>
       <c r="B589" s="1" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="C589" s="2">
         <v>902</v>
@@ -18805,7 +18805,7 @@
         <v>7501109763375</v>
       </c>
       <c r="B590" s="1" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="C590" s="2">
         <v>903</v>
@@ -18828,7 +18828,7 @@
         <v>7502216791619</v>
       </c>
       <c r="B591" s="1" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="C591" s="2">
         <v>904</v>
@@ -18897,7 +18897,7 @@
         <v>7501349027060</v>
       </c>
       <c r="B594" s="1" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="C594" s="2">
         <v>907</v>
@@ -18920,7 +18920,7 @@
         <v>7501349025059</v>
       </c>
       <c r="B595" s="1" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="C595" s="2">
         <v>908</v>
@@ -19058,7 +19058,7 @@
         <v>7502227876398</v>
       </c>
       <c r="B601" s="1" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="C601" s="2">
         <v>914</v>
@@ -19219,7 +19219,7 @@
         <v>7502216790896</v>
       </c>
       <c r="B608" s="1" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="C608" s="2">
         <v>978</v>
@@ -19242,7 +19242,7 @@
         <v>821998000571</v>
       </c>
       <c r="B609" s="1" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="C609" s="2">
         <v>979</v>
@@ -19587,7 +19587,7 @@
         <v>5601332</v>
       </c>
       <c r="B624" s="1" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="C624" s="2">
         <v>1051</v>
@@ -19978,7 +19978,7 @@
         <v>7501349021624</v>
       </c>
       <c r="B641" s="1" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="C641" s="2">
         <v>1115</v>
@@ -20599,7 +20599,7 @@
         <v>714908107098</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="C668" s="2">
         <v>9002</v>
@@ -20668,7 +20668,7 @@
         <v>714908105483</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="C671" s="2">
         <v>9009</v>
@@ -20691,7 +20691,7 @@
         <v>7501258206723</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="C672" s="2">
         <v>9013</v>
@@ -20829,7 +20829,7 @@
         <v>7502214010415</v>
       </c>
       <c r="B678" s="1" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="C678" s="2">
         <v>9021</v>
@@ -20921,7 +20921,7 @@
         <v>7502214011054</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="C682" s="2">
         <v>9031</v>
@@ -20967,7 +20967,7 @@
         <v>7502214011030</v>
       </c>
       <c r="B684" s="1" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="C684" s="2">
         <v>9033</v>
@@ -21036,7 +21036,7 @@
         <v>7502214010347</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="C687" s="2">
         <v>9038</v>
@@ -21082,7 +21082,7 @@
         <v>75035000242</v>
       </c>
       <c r="B689" s="1" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="C689" s="2">
         <v>9051</v>
@@ -21105,7 +21105,7 @@
         <v>7502244010126</v>
       </c>
       <c r="B690" s="1" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="C690" s="2">
         <v>9054</v>
@@ -21220,7 +21220,7 @@
         <v>7503007662194</v>
       </c>
       <c r="B695" s="1" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="C695" s="2">
         <v>9069</v>
@@ -21243,7 +21243,7 @@
         <v>7503007662255</v>
       </c>
       <c r="B696" s="1" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="C696" s="2">
         <v>9070</v>
@@ -21312,7 +21312,7 @@
         <v>7502214011023</v>
       </c>
       <c r="B699" s="1" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="C699" s="2">
         <v>9078</v>
@@ -21404,7 +21404,7 @@
         <v>7502010840193</v>
       </c>
       <c r="B703" s="1" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="C703" s="2">
         <v>9086</v>
@@ -21427,7 +21427,7 @@
         <v>7503007202437</v>
       </c>
       <c r="B704" s="1" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="C704" s="2">
         <v>9089</v>
@@ -21519,7 +21519,7 @@
         <v>803288480669</v>
       </c>
       <c r="B708" s="1" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="C708" s="2">
         <v>9107</v>
@@ -21542,7 +21542,7 @@
         <v>714908100099</v>
       </c>
       <c r="B709" s="1" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="C709" s="2">
         <v>9108</v>
@@ -21634,7 +21634,7 @@
         <v>7502010840292</v>
       </c>
       <c r="B713" s="1" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="C713" s="2">
         <v>9120</v>
@@ -21680,7 +21680,7 @@
         <v>7501384504939</v>
       </c>
       <c r="B715" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="C715" s="2">
         <v>9137</v>
@@ -21703,7 +21703,7 @@
         <v>7501590283048</v>
       </c>
       <c r="B716" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="C716" s="2">
         <v>9138</v>
@@ -21772,7 +21772,7 @@
         <v>714908100518</v>
       </c>
       <c r="B719" s="1" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="C719" s="2">
         <v>9146</v>
@@ -21795,7 +21795,7 @@
         <v>7502009743993</v>
       </c>
       <c r="B720" s="1" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="C720" s="2">
         <v>9147</v>
@@ -21933,7 +21933,7 @@
         <v>7503181042881</v>
       </c>
       <c r="B726" s="1" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="C726" s="2">
         <v>9173</v>
@@ -22071,7 +22071,7 @@
         <v>7501075712223</v>
       </c>
       <c r="B732" s="1" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="C732" s="2">
         <v>9193</v>
@@ -22094,7 +22094,7 @@
         <v>7500326106972</v>
       </c>
       <c r="B733" s="1" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="C733" s="2">
         <v>9195</v>
@@ -22163,7 +22163,7 @@
         <v>7503008344150</v>
       </c>
       <c r="B736" s="1" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="C736" s="2">
         <v>9199</v>
@@ -22278,7 +22278,7 @@
         <v>7502259891376</v>
       </c>
       <c r="B741" s="1" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="C741" s="2">
         <v>9227</v>
@@ -22347,7 +22347,7 @@
         <v>7502259891079</v>
       </c>
       <c r="B744" s="1" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="C744" s="2">
         <v>9234</v>
@@ -22577,7 +22577,7 @@
         <v>714908100822</v>
       </c>
       <c r="B754" s="1" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="C754" s="2">
         <v>9291</v>
@@ -22669,7 +22669,7 @@
         <v>7503011998753</v>
       </c>
       <c r="B758" s="1" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="C758" s="2">
         <v>9305</v>
@@ -22692,7 +22692,7 @@
         <v>7503011998760</v>
       </c>
       <c r="B759" s="1" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="C759" s="2">
         <v>9306</v>
@@ -22715,7 +22715,7 @@
         <v>7503011998746</v>
       </c>
       <c r="B760" s="1" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="C760" s="2">
         <v>9307</v>
@@ -22761,7 +22761,7 @@
         <v>7503000812015</v>
       </c>
       <c r="B762" s="1" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="C762" s="2">
         <v>9325</v>
@@ -22876,7 +22876,7 @@
         <v>7500326106989</v>
       </c>
       <c r="B767" s="1" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="C767" s="2">
         <v>9341</v>
@@ -22899,7 +22899,7 @@
         <v>7500326108747</v>
       </c>
       <c r="B768" s="1" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="C768" s="2">
         <v>9343</v>
@@ -23037,7 +23037,7 @@
         <v>803288480218</v>
       </c>
       <c r="B774" s="1" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="C774" s="2">
         <v>9363</v>
@@ -23060,7 +23060,7 @@
         <v>803288480737</v>
       </c>
       <c r="B775" s="1" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="C775" s="2">
         <v>9385</v>
@@ -23129,7 +23129,7 @@
         <v>7501130704231</v>
       </c>
       <c r="B778" s="1" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="C778" s="2">
         <v>9447</v>
@@ -23451,7 +23451,7 @@
         <v>631758002192</v>
       </c>
       <c r="B792" s="1" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="C792" s="2">
         <v>9500</v>
@@ -23474,7 +23474,7 @@
         <v>750350000402</v>
       </c>
       <c r="B793" s="1" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="C793" s="2">
         <v>9505</v>
@@ -23681,7 +23681,7 @@
         <v>7502001165489</v>
       </c>
       <c r="B802" s="1" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="C802" s="2">
         <v>9594</v>
@@ -23704,7 +23704,7 @@
         <v>7501590284335</v>
       </c>
       <c r="B803" s="1" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="C803" s="2">
         <v>9622</v>
@@ -23727,7 +23727,7 @@
         <v>7500462199586</v>
       </c>
       <c r="B804" s="1" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="C804" s="2">
         <v>9632</v>
@@ -23750,7 +23750,7 @@
         <v>7500462199685</v>
       </c>
       <c r="B805" s="1" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="C805" s="2">
         <v>9633</v>
@@ -23773,7 +23773,7 @@
         <v>7500462199692</v>
       </c>
       <c r="B806" s="1" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="C806" s="2">
         <v>9634</v>
@@ -23865,7 +23865,7 @@
         <v>750104003574</v>
       </c>
       <c r="B810" s="1" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="C810" s="2">
         <v>9704</v>
@@ -23888,7 +23888,7 @@
         <v>750104003574</v>
       </c>
       <c r="B811" s="1" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="C811" s="2">
         <v>9704</v>
@@ -23911,7 +23911,7 @@
         <v>7502275940065</v>
       </c>
       <c r="B812" s="1" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="C812" s="2">
         <v>9705</v>
@@ -23934,7 +23934,7 @@
         <v>750104002027</v>
       </c>
       <c r="B813" s="1" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="C813" s="2">
         <v>9707</v>
@@ -23957,7 +23957,7 @@
         <v>750104003314</v>
       </c>
       <c r="B814" s="1" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="C814" s="2">
         <v>9709</v>
@@ -24003,7 +24003,7 @@
         <v>7502007700226</v>
       </c>
       <c r="B816" s="1" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="C816" s="2">
         <v>9715</v>
@@ -24026,7 +24026,7 @@
         <v>7502007700271</v>
       </c>
       <c r="B817" s="1" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="C817" s="2">
         <v>9716</v>
@@ -24095,7 +24095,7 @@
         <v>714908105957</v>
       </c>
       <c r="B820" s="1" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="C820" s="2">
         <v>9731</v>
@@ -24118,7 +24118,7 @@
         <v>7501172018228</v>
       </c>
       <c r="B821" s="1" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="C821" s="2">
         <v>9733</v>
@@ -24187,7 +24187,7 @@
         <v>7501825300885</v>
       </c>
       <c r="B824" s="1" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="C824" s="2">
         <v>9737</v>
@@ -24210,7 +24210,7 @@
         <v>7503008344617</v>
       </c>
       <c r="B825" s="1" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="C825" s="2">
         <v>9738</v>
@@ -24233,7 +24233,7 @@
         <v>7503002047620</v>
       </c>
       <c r="B826" s="1" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="C826" s="2">
         <v>9739</v>
@@ -24279,7 +24279,7 @@
         <v>7502010840360</v>
       </c>
       <c r="B828" s="1" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="C828" s="2">
         <v>9745</v>
@@ -24302,7 +24302,7 @@
         <v>7501060808016</v>
       </c>
       <c r="B829" s="1" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C829" s="2">
         <v>9747</v>
@@ -24394,7 +24394,7 @@
         <v>7502001164338</v>
       </c>
       <c r="B833" s="1" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="C833" s="2">
         <v>9771</v>
@@ -24463,7 +24463,7 @@
         <v>7501258207010</v>
       </c>
       <c r="B836" s="1" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="C836" s="2">
         <v>9780</v>
@@ -24509,7 +24509,7 @@
         <v>7502280810605</v>
       </c>
       <c r="B838" s="1" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="C838" s="2">
         <v>9782</v>
@@ -24532,7 +24532,7 @@
         <v>7502280810056</v>
       </c>
       <c r="B839" s="1" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="C839" s="2">
         <v>9783</v>
@@ -24831,7 +24831,7 @@
         <v>7502314550002</v>
       </c>
       <c r="B852" s="1" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="C852" s="2">
         <v>9822</v>
@@ -24877,7 +24877,7 @@
         <v>7502227421666</v>
       </c>
       <c r="B854" s="1" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="C854" s="2">
         <v>9842</v>
@@ -24900,7 +24900,7 @@
         <v>7500462933746</v>
       </c>
       <c r="B855" s="1" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="C855" s="2">
         <v>9843</v>
@@ -25038,7 +25038,7 @@
         <v>7506021101564</v>
       </c>
       <c r="B861" s="1" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="C861" s="2">
         <v>9849</v>
@@ -25084,7 +25084,7 @@
         <v>7501130711642</v>
       </c>
       <c r="B863" s="1" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="C863" s="2">
         <v>9854</v>
@@ -25130,7 +25130,7 @@
         <v>750113071868</v>
       </c>
       <c r="B865" s="1" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="C865" s="2">
         <v>9856</v>
@@ -25153,7 +25153,7 @@
         <v>7506021100710</v>
       </c>
       <c r="B866" s="1" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="C866" s="2">
         <v>9858</v>
@@ -25245,7 +25245,7 @@
         <v>7506504900592</v>
       </c>
       <c r="B870" s="1" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="C870" s="2">
         <v>9865</v>
@@ -25268,7 +25268,7 @@
         <v>7502214018350</v>
       </c>
       <c r="B871" s="1" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="C871" s="2">
         <v>9866</v>
@@ -25659,7 +25659,7 @@
         <v>759684191077</v>
       </c>
       <c r="B888" s="1" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="C888" s="2">
         <v>9883</v>
@@ -26188,7 +26188,7 @@
         <v>7502259892250</v>
       </c>
       <c r="B911" s="1" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C911" s="2">
         <v>9915</v>
@@ -26487,7 +26487,7 @@
         <v>731416423427</v>
       </c>
       <c r="B924" s="1" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C924" s="2">
         <v>9928</v>
@@ -27062,7 +27062,7 @@
         <v>677144634059</v>
       </c>
       <c r="B949" s="1" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C949" s="2">
         <v>9970</v>
@@ -27085,7 +27085,7 @@
         <v>731416423427</v>
       </c>
       <c r="B950" s="1" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C950" s="2">
         <v>9971</v>
@@ -27505,7 +27505,7 @@
         <v>1143</v>
       </c>
       <c r="D968" s="2" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="E968" s="13" t="s">
         <v>23</v>
@@ -27528,7 +27528,7 @@
         <v>9990</v>
       </c>
       <c r="D969" s="16" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="E969" s="2" t="s">
         <v>23</v>
@@ -27551,7 +27551,7 @@
         <v>9991</v>
       </c>
       <c r="D970" s="16" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="E970" s="2" t="s">
         <v>23</v>
@@ -27574,7 +27574,7 @@
         <v>9794</v>
       </c>
       <c r="D971" s="16" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="E971" s="2" t="s">
         <v>23</v>
@@ -27597,7 +27597,7 @@
         <v>9992</v>
       </c>
       <c r="D972" s="16" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="E972" s="2" t="s">
         <v>23</v>
@@ -27620,7 +27620,7 @@
         <v>9993</v>
       </c>
       <c r="D973" s="16" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="E973" s="2" t="s">
         <v>23</v>
@@ -27643,7 +27643,7 @@
         <v>9994</v>
       </c>
       <c r="D974" s="16" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="E974" s="2" t="s">
         <v>23</v>
@@ -27666,7 +27666,7 @@
         <v>9995</v>
       </c>
       <c r="D975" s="16" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="E975" s="2" t="s">
         <v>23</v>

--- a/posiciones_buscador.xlsx
+++ b/posiciones_buscador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\desarrollos\buscador_posiciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F1209B-6E85-4A5F-9DBB-B9E7607CFE66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC49A00-DB21-4B03-A7B9-F4BC4585AC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81345FCE-0991-44B1-AB97-4BC767A118BC}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4877" uniqueCount="1544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4887" uniqueCount="1546">
   <si>
     <t>Cod. De Barras</t>
   </si>
@@ -4571,9 +4571,6 @@
     <t>7502007700271, 7502275940171</t>
   </si>
   <si>
-    <t>714908107920</t>
-  </si>
-  <si>
     <t>7502214013089</t>
   </si>
   <si>
@@ -4671,6 +4668,15 @@
   </si>
   <si>
     <t>7503003406242, 7506346600308, 75968431605, 6650376816114</t>
+  </si>
+  <si>
+    <t>714908107920, 714908105940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URBA BILOB CAPSULAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIFLOSENSI DAPAGLIFLOZINA 10 MG C/28 </t>
   </si>
 </sst>
 </file>
@@ -4908,8 +4914,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G975" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G975" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G977" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G977" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G967">
     <sortCondition ref="C1:C967"/>
   </sortState>
@@ -5245,7 +5251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD76C0E-5FFA-48DF-BC8E-37CFF7587C46}">
-  <dimension ref="A1:G975"/>
+  <dimension ref="A1:G977"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
@@ -16206,7 +16212,7 @@
         <v>7503003406242</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="C477" s="2">
         <v>683</v>
@@ -24095,7 +24101,7 @@
         <v>714908105957</v>
       </c>
       <c r="B820" s="1" t="s">
-        <v>1510</v>
+        <v>1543</v>
       </c>
       <c r="C820" s="2">
         <v>9731</v>
@@ -24118,7 +24124,7 @@
         <v>7501172018228</v>
       </c>
       <c r="B821" s="1" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="C821" s="2">
         <v>9733</v>
@@ -24187,7 +24193,7 @@
         <v>7501825300885</v>
       </c>
       <c r="B824" s="1" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="C824" s="2">
         <v>9737</v>
@@ -24210,7 +24216,7 @@
         <v>7503008344617</v>
       </c>
       <c r="B825" s="1" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="C825" s="2">
         <v>9738</v>
@@ -24233,7 +24239,7 @@
         <v>7503002047620</v>
       </c>
       <c r="B826" s="1" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="C826" s="2">
         <v>9739</v>
@@ -24279,7 +24285,7 @@
         <v>7502010840360</v>
       </c>
       <c r="B828" s="1" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="C828" s="2">
         <v>9745</v>
@@ -24302,7 +24308,7 @@
         <v>7501060808016</v>
       </c>
       <c r="B829" s="1" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="C829" s="2">
         <v>9747</v>
@@ -24394,7 +24400,7 @@
         <v>7502001164338</v>
       </c>
       <c r="B833" s="1" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C833" s="2">
         <v>9771</v>
@@ -24463,7 +24469,7 @@
         <v>7501258207010</v>
       </c>
       <c r="B836" s="1" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="C836" s="2">
         <v>9780</v>
@@ -24509,7 +24515,7 @@
         <v>7502280810605</v>
       </c>
       <c r="B838" s="1" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="C838" s="2">
         <v>9782</v>
@@ -24532,7 +24538,7 @@
         <v>7502280810056</v>
       </c>
       <c r="B839" s="1" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="C839" s="2">
         <v>9783</v>
@@ -24831,7 +24837,7 @@
         <v>7502314550002</v>
       </c>
       <c r="B852" s="1" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="C852" s="2">
         <v>9822</v>
@@ -24877,7 +24883,7 @@
         <v>7502227421666</v>
       </c>
       <c r="B854" s="1" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="C854" s="2">
         <v>9842</v>
@@ -24900,7 +24906,7 @@
         <v>7500462933746</v>
       </c>
       <c r="B855" s="1" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="C855" s="2">
         <v>9843</v>
@@ -25038,7 +25044,7 @@
         <v>7506021101564</v>
       </c>
       <c r="B861" s="1" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="C861" s="2">
         <v>9849</v>
@@ -25084,7 +25090,7 @@
         <v>7501130711642</v>
       </c>
       <c r="B863" s="1" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="C863" s="2">
         <v>9854</v>
@@ -25130,7 +25136,7 @@
         <v>750113071868</v>
       </c>
       <c r="B865" s="1" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="C865" s="2">
         <v>9856</v>
@@ -25153,7 +25159,7 @@
         <v>7506021100710</v>
       </c>
       <c r="B866" s="1" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="C866" s="2">
         <v>9858</v>
@@ -25245,7 +25251,7 @@
         <v>7506504900592</v>
       </c>
       <c r="B870" s="1" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="C870" s="2">
         <v>9865</v>
@@ -25268,7 +25274,7 @@
         <v>7502214018350</v>
       </c>
       <c r="B871" s="1" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="C871" s="2">
         <v>9866</v>
@@ -25659,7 +25665,7 @@
         <v>759684191077</v>
       </c>
       <c r="B888" s="1" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="C888" s="2">
         <v>9883</v>
@@ -26188,7 +26194,7 @@
         <v>7502259892250</v>
       </c>
       <c r="B911" s="1" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="C911" s="2">
         <v>9915</v>
@@ -26487,7 +26493,7 @@
         <v>731416423427</v>
       </c>
       <c r="B924" s="1" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C924" s="2">
         <v>9928</v>
@@ -27062,7 +27068,7 @@
         <v>677144634059</v>
       </c>
       <c r="B949" s="1" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C949" s="2">
         <v>9970</v>
@@ -27085,7 +27091,7 @@
         <v>731416423427</v>
       </c>
       <c r="B950" s="1" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C950" s="2">
         <v>9971</v>
@@ -27505,7 +27511,7 @@
         <v>1143</v>
       </c>
       <c r="D968" s="2" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="E968" s="13" t="s">
         <v>23</v>
@@ -27528,7 +27534,7 @@
         <v>9990</v>
       </c>
       <c r="D969" s="16" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="E969" s="2" t="s">
         <v>23</v>
@@ -27551,7 +27557,7 @@
         <v>9991</v>
       </c>
       <c r="D970" s="16" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="E970" s="2" t="s">
         <v>23</v>
@@ -27574,7 +27580,7 @@
         <v>9794</v>
       </c>
       <c r="D971" s="16" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="E971" s="2" t="s">
         <v>23</v>
@@ -27597,7 +27603,7 @@
         <v>9992</v>
       </c>
       <c r="D972" s="16" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="E972" s="2" t="s">
         <v>23</v>
@@ -27620,7 +27626,7 @@
         <v>9993</v>
       </c>
       <c r="D973" s="16" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="E973" s="2" t="s">
         <v>23</v>
@@ -27643,7 +27649,7 @@
         <v>9994</v>
       </c>
       <c r="D974" s="16" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="E974" s="2" t="s">
         <v>23</v>
@@ -27662,11 +27668,11 @@
       <c r="B975" s="12" t="s">
         <v>999</v>
       </c>
-      <c r="C975" s="22">
+      <c r="C975" s="16">
         <v>9995</v>
       </c>
       <c r="D975" s="16" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="E975" s="2" t="s">
         <v>23</v>
@@ -27675,13 +27681,59 @@
         <v>12</v>
       </c>
       <c r="G975" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="976" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A976" s="1">
+        <v>7500104003116</v>
+      </c>
+      <c r="B976" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C976" s="16">
+        <v>9725</v>
+      </c>
+      <c r="D976" s="16" t="s">
+        <v>1544</v>
+      </c>
+      <c r="E976" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F976" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G976" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="977" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A977" s="1">
+        <v>7506022331502</v>
+      </c>
+      <c r="B977" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C977" s="22">
+        <v>1146</v>
+      </c>
+      <c r="D977" s="16" t="s">
+        <v>1545</v>
+      </c>
+      <c r="E977" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F977" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G977" s="2" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="D2:D969 D970:D975" calculatedColumn="1"/>
+    <ignoredError sqref="D2:D977" calculatedColumn="1"/>
     <ignoredError sqref="B949:B950" numberStoredAsText="1"/>
   </ignoredErrors>
   <tableParts count="1">

--- a/posiciones_buscador.xlsx
+++ b/posiciones_buscador.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\desarrollos\buscador_posiciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC49A00-DB21-4B03-A7B9-F4BC4585AC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8EE3F9C-F2E6-49A5-8799-CED733949AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81345FCE-0991-44B1-AB97-4BC767A118BC}"/>
+    <workbookView xWindow="-17835" yWindow="0" windowWidth="17940" windowHeight="15585" xr2:uid="{81345FCE-0991-44B1-AB97-4BC767A118BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Productos_posicion (2)" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4887" uniqueCount="1546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4940" uniqueCount="1556">
   <si>
     <t>Cod. De Barras</t>
   </si>
@@ -4677,6 +4677,36 @@
   </si>
   <si>
     <t xml:space="preserve">DIFLOSENSI DAPAGLIFLOZINA 10 MG C/28 </t>
+  </si>
+  <si>
+    <t>LUBRICANTE 75 ML PRUDENCE LUB SABOR GROSELLA</t>
+  </si>
+  <si>
+    <t>UB S3  COMPLEX C/60 500 MG</t>
+  </si>
+  <si>
+    <t>UB DOL-F COMPLEX C/30 500 MG</t>
+  </si>
+  <si>
+    <t>UB LXT TAMARINDO CIRUELA Y LINAZA</t>
+  </si>
+  <si>
+    <t>UB CPU 500 MG C/60</t>
+  </si>
+  <si>
+    <t>UB VITAMINA  E</t>
+  </si>
+  <si>
+    <t>UB ACIDO ALFA LIPOICO</t>
+  </si>
+  <si>
+    <t>UB CITRATO DE POTASIO 500MG C/60</t>
+  </si>
+  <si>
+    <t>UB ZINC 50 MG C/100</t>
+  </si>
+  <si>
+    <t>ACEITE DE MAGNESIO</t>
   </si>
 </sst>
 </file>
@@ -4914,8 +4944,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G977" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G977" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G988" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G988" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G967">
     <sortCondition ref="C1:C967"/>
   </sortState>
@@ -5251,7 +5281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD76C0E-5FFA-48DF-BC8E-37CFF7587C46}">
-  <dimension ref="A1:G977"/>
+  <dimension ref="A1:G988"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
@@ -27714,7 +27744,7 @@
       <c r="B977" s="12" t="s">
         <v>999</v>
       </c>
-      <c r="C977" s="22">
+      <c r="C977" s="16">
         <v>1146</v>
       </c>
       <c r="D977" s="16" t="s">
@@ -27728,12 +27758,265 @@
       </c>
       <c r="G977" s="2" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="978" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A978" s="20">
+        <v>7500104003116</v>
+      </c>
+      <c r="B978" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C978" s="16">
+        <v>9725</v>
+      </c>
+      <c r="D978" s="16" t="s">
+        <v>1544</v>
+      </c>
+      <c r="E978" t="s">
+        <v>22</v>
+      </c>
+      <c r="F978" t="s">
+        <v>17</v>
+      </c>
+      <c r="G978" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="979" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A979" s="20">
+        <v>7502214983153</v>
+      </c>
+      <c r="B979" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C979" s="16">
+        <v>626</v>
+      </c>
+      <c r="D979" s="16" t="s">
+        <v>1546</v>
+      </c>
+      <c r="E979" t="s">
+        <v>23</v>
+      </c>
+      <c r="F979" t="s">
+        <v>24</v>
+      </c>
+      <c r="G979" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="980" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A980" s="20">
+        <v>7502275940638</v>
+      </c>
+      <c r="B980" s="7">
+        <v>7502275940263</v>
+      </c>
+      <c r="C980" s="16">
+        <v>9728</v>
+      </c>
+      <c r="D980" s="16" t="s">
+        <v>1547</v>
+      </c>
+      <c r="E980" t="s">
+        <v>22</v>
+      </c>
+      <c r="F980" t="s">
+        <v>12</v>
+      </c>
+      <c r="G980" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="981" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A981" s="20">
+        <v>7502275940621</v>
+      </c>
+      <c r="B981" s="7">
+        <v>7502275940430</v>
+      </c>
+      <c r="C981" s="16">
+        <v>9708</v>
+      </c>
+      <c r="D981" s="16" t="s">
+        <v>1548</v>
+      </c>
+      <c r="E981" t="s">
+        <v>22</v>
+      </c>
+      <c r="F981" t="s">
+        <v>13</v>
+      </c>
+      <c r="G981" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="982" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A982" s="20">
+        <v>7502275940393</v>
+      </c>
+      <c r="B982" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C982" s="16">
+        <v>9710</v>
+      </c>
+      <c r="D982" s="16" t="s">
+        <v>1549</v>
+      </c>
+      <c r="E982" t="s">
+        <v>22</v>
+      </c>
+      <c r="F982" t="s">
+        <v>12</v>
+      </c>
+      <c r="G982" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="983" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A983" s="20">
+        <v>7502275940447</v>
+      </c>
+      <c r="B983" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C983" s="16">
+        <v>9998</v>
+      </c>
+      <c r="D983" s="16" t="s">
+        <v>1550</v>
+      </c>
+      <c r="E983" t="s">
+        <v>23</v>
+      </c>
+      <c r="F983" t="s">
+        <v>6</v>
+      </c>
+      <c r="G983" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="984" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A984" s="20">
+        <v>7502275940140</v>
+      </c>
+      <c r="B984" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C984" s="16">
+        <v>9996</v>
+      </c>
+      <c r="D984" s="16" t="s">
+        <v>1551</v>
+      </c>
+      <c r="E984" t="s">
+        <v>23</v>
+      </c>
+      <c r="F984" t="s">
+        <v>13</v>
+      </c>
+      <c r="G984" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="985" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A985" s="20">
+        <v>7502275940577</v>
+      </c>
+      <c r="B985" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C985" s="16">
+        <v>9999</v>
+      </c>
+      <c r="D985" s="16" t="s">
+        <v>1552</v>
+      </c>
+      <c r="E985" t="s">
+        <v>23</v>
+      </c>
+      <c r="F985" t="s">
+        <v>15</v>
+      </c>
+      <c r="G985" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="986" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A986" s="20">
+        <v>7502275940553</v>
+      </c>
+      <c r="B986" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C986" s="16">
+        <v>99100</v>
+      </c>
+      <c r="D986" s="16" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E986" t="s">
+        <v>23</v>
+      </c>
+      <c r="F986" t="s">
+        <v>24</v>
+      </c>
+      <c r="G986" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="987" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A987" s="20">
+        <v>7502275940591</v>
+      </c>
+      <c r="B987" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C987" s="16">
+        <v>9997</v>
+      </c>
+      <c r="D987" s="16" t="s">
+        <v>1554</v>
+      </c>
+      <c r="E987" t="s">
+        <v>22</v>
+      </c>
+      <c r="F987" t="s">
+        <v>16</v>
+      </c>
+      <c r="G987" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="988" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A988" s="20">
+        <v>7502275940676</v>
+      </c>
+      <c r="B988" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C988" s="22">
+        <v>99101</v>
+      </c>
+      <c r="D988" s="16" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E988" t="s">
+        <v>22</v>
+      </c>
+      <c r="F988" t="s">
+        <v>16</v>
+      </c>
+      <c r="G988" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="D2:D977" calculatedColumn="1"/>
+    <ignoredError sqref="D2:D977 D978:D988" calculatedColumn="1"/>
     <ignoredError sqref="B949:B950" numberStoredAsText="1"/>
   </ignoredErrors>
   <tableParts count="1">

--- a/posiciones_buscador.xlsx
+++ b/posiciones_buscador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\desarrollos\buscador_posiciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C35E4F-AC4F-4BAD-948F-FD53719E0FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1648CA-D48E-40E9-8E7F-86B63F268478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81345FCE-0991-44B1-AB97-4BC767A118BC}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="1725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6108" uniqueCount="1726">
   <si>
     <t>Cod. De Barras</t>
   </si>
@@ -5219,6 +5219,9 @@
   </si>
   <si>
     <t>7502259891109, 7502259891116</t>
+  </si>
+  <si>
+    <t>ELECTROLITOS APO</t>
   </si>
 </sst>
 </file>
@@ -5488,8 +5491,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G998" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G998" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G999" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G999" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G967">
     <sortCondition ref="C1:C967"/>
   </sortState>
@@ -5825,7 +5828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD76C0E-5FFA-48DF-BC8E-37CFF7587C46}">
-  <dimension ref="A1:G998"/>
+  <dimension ref="A1:G999"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
@@ -28771,7 +28774,7 @@
       <c r="B998" s="12" t="s">
         <v>999</v>
       </c>
-      <c r="C998" s="22">
+      <c r="C998" s="16">
         <v>418</v>
       </c>
       <c r="D998" s="16" t="s">
@@ -28785,12 +28788,35 @@
       </c>
       <c r="G998" s="2" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="999" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A999" s="1">
+        <v>7501277032303</v>
+      </c>
+      <c r="B999" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C999" s="22">
+        <v>11101</v>
+      </c>
+      <c r="D999" s="16" t="s">
+        <v>1725</v>
+      </c>
+      <c r="E999" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F999" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G999" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="D2:D977 D978:D987 D988:D998" calculatedColumn="1"/>
+    <ignoredError sqref="D2:D977 D978:D999" calculatedColumn="1"/>
     <ignoredError sqref="B949:B950" numberStoredAsText="1"/>
   </ignoredErrors>
   <tableParts count="1">

--- a/posiciones_buscador.xlsx
+++ b/posiciones_buscador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\desarrollos\buscador_posiciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1648CA-D48E-40E9-8E7F-86B63F268478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC0C40A-FBAC-4B31-BD92-0C807FE4AD6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81345FCE-0991-44B1-AB97-4BC767A118BC}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6108" uniqueCount="1726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6112" uniqueCount="1726">
   <si>
     <t>Cod. De Barras</t>
   </si>
@@ -5491,8 +5491,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G999" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G999" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G1000" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G1000" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G967">
     <sortCondition ref="C1:C967"/>
   </sortState>
@@ -5828,7 +5828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD76C0E-5FFA-48DF-BC8E-37CFF7587C46}">
-  <dimension ref="A1:G999"/>
+  <dimension ref="A1:G1000"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
@@ -28797,7 +28797,7 @@
       <c r="B999" s="12" t="s">
         <v>999</v>
       </c>
-      <c r="C999" s="22">
+      <c r="C999" s="16">
         <v>11101</v>
       </c>
       <c r="D999" s="16" t="s">
@@ -28811,12 +28811,35 @@
       </c>
       <c r="G999" s="2" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1000" s="1">
+        <v>7501825300878</v>
+      </c>
+      <c r="B1000" s="7">
+        <v>75006464</v>
+      </c>
+      <c r="C1000" s="22">
+        <v>476</v>
+      </c>
+      <c r="D1000" s="16" t="s">
+        <v>1581</v>
+      </c>
+      <c r="E1000" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1000" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1000" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="D2:D977 D978:D999" calculatedColumn="1"/>
+    <ignoredError sqref="D2:D1000" calculatedColumn="1"/>
     <ignoredError sqref="B949:B950" numberStoredAsText="1"/>
   </ignoredErrors>
   <tableParts count="1">

--- a/posiciones_buscador.xlsx
+++ b/posiciones_buscador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\desarrollos\buscador_posiciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC0C40A-FBAC-4B31-BD92-0C807FE4AD6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246D3D4B-6457-4C4A-812B-4D211EE4C3CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81345FCE-0991-44B1-AB97-4BC767A118BC}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6112" uniqueCount="1726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6116" uniqueCount="1726">
   <si>
     <t>Cod. De Barras</t>
   </si>
@@ -5491,8 +5491,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G1000" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G1000" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G1001" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G1001" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G967">
     <sortCondition ref="C1:C967"/>
   </sortState>
@@ -5828,7 +5828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD76C0E-5FFA-48DF-BC8E-37CFF7587C46}">
-  <dimension ref="A1:G1000"/>
+  <dimension ref="A1:G1001"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
@@ -28820,7 +28820,7 @@
       <c r="B1000" s="7">
         <v>75006464</v>
       </c>
-      <c r="C1000" s="22">
+      <c r="C1000" s="16">
         <v>476</v>
       </c>
       <c r="D1000" s="16" t="s">
@@ -28834,12 +28834,35 @@
       </c>
       <c r="G1000" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1001" s="1">
+        <v>123456789123</v>
+      </c>
+      <c r="B1001" s="7">
+        <v>750336200468</v>
+      </c>
+      <c r="C1001" s="22">
+        <v>9478</v>
+      </c>
+      <c r="D1001" s="16" t="s">
+        <v>1613</v>
+      </c>
+      <c r="E1001" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1001" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1001" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="D2:D1000" calculatedColumn="1"/>
+    <ignoredError sqref="D2:D1001" calculatedColumn="1"/>
     <ignoredError sqref="B949:B950" numberStoredAsText="1"/>
   </ignoredErrors>
   <tableParts count="1">

--- a/posiciones_buscador.xlsx
+++ b/posiciones_buscador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\desarrollos\buscador_posiciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246D3D4B-6457-4C4A-812B-4D211EE4C3CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D990E363-5896-4BAA-B15E-FFCCA0220C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81345FCE-0991-44B1-AB97-4BC767A118BC}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6116" uniqueCount="1726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6121" uniqueCount="1727">
   <si>
     <t>Cod. De Barras</t>
   </si>
@@ -5222,6 +5222,9 @@
   </si>
   <si>
     <t>ELECTROLITOS APO</t>
+  </si>
+  <si>
+    <t>NITROFURANTOINA SURONIT  100 MG C/12</t>
   </si>
 </sst>
 </file>
@@ -5491,8 +5494,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G1001" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G1001" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G1002" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G1002" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G967">
     <sortCondition ref="C1:C967"/>
   </sortState>
@@ -5828,7 +5831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD76C0E-5FFA-48DF-BC8E-37CFF7587C46}">
-  <dimension ref="A1:G1001"/>
+  <dimension ref="A1:G1002"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
@@ -28843,7 +28846,7 @@
       <c r="B1001" s="7">
         <v>750336200468</v>
       </c>
-      <c r="C1001" s="22">
+      <c r="C1001" s="16">
         <v>9478</v>
       </c>
       <c r="D1001" s="16" t="s">
@@ -28857,6 +28860,29 @@
       </c>
       <c r="G1001" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1002" s="20">
+        <v>7501825300823</v>
+      </c>
+      <c r="B1002" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C1002" s="22">
+        <v>1149</v>
+      </c>
+      <c r="D1002" s="16" t="s">
+        <v>1726</v>
+      </c>
+      <c r="E1002" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1002" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1002" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/posiciones_buscador.xlsx
+++ b/posiciones_buscador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\desarrollos\buscador_posiciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D990E363-5896-4BAA-B15E-FFCCA0220C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D5F774A-2F17-4E6D-B998-8CDFCEF421F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81345FCE-0991-44B1-AB97-4BC767A118BC}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6121" uniqueCount="1727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6126" uniqueCount="1727">
   <si>
     <t>Cod. De Barras</t>
   </si>
@@ -5494,8 +5494,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G1002" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G1002" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G1003" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G1003" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G967">
     <sortCondition ref="C1:C967"/>
   </sortState>
@@ -5831,7 +5831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD76C0E-5FFA-48DF-BC8E-37CFF7587C46}">
-  <dimension ref="A1:G1002"/>
+  <dimension ref="A1:G1003"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
@@ -28869,7 +28869,7 @@
       <c r="B1002" s="12" t="s">
         <v>999</v>
       </c>
-      <c r="C1002" s="22">
+      <c r="C1002" s="16">
         <v>1149</v>
       </c>
       <c r="D1002" s="16" t="s">
@@ -28882,13 +28882,36 @@
         <v>16</v>
       </c>
       <c r="G1002" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1003" s="20">
+        <v>7506452400038</v>
+      </c>
+      <c r="B1003" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C1003" s="22">
+        <v>9916</v>
+      </c>
+      <c r="D1003" s="16" t="s">
+        <v>912</v>
+      </c>
+      <c r="E1003" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1003" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1003" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="D2:D1001" calculatedColumn="1"/>
+    <ignoredError sqref="D2:D1001 D1002:D1003" calculatedColumn="1"/>
     <ignoredError sqref="B949:B950" numberStoredAsText="1"/>
   </ignoredErrors>
   <tableParts count="1">

--- a/posiciones_buscador.xlsx
+++ b/posiciones_buscador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\desarrollos\buscador_posiciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA5A58CA-E36C-4E45-9103-578D6356E522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB67A41-37E5-4BE2-BC94-0FC2CA744F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81345FCE-0991-44B1-AB97-4BC767A118BC}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6121" uniqueCount="1718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6132" uniqueCount="1718">
   <si>
     <t>Cod. De Barras</t>
   </si>
@@ -5477,8 +5477,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G1021" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G1021" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G1022" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G1022" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G967">
     <sortCondition ref="C1:C967"/>
   </sortState>
@@ -5814,7 +5814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD76C0E-5FFA-48DF-BC8E-37CFF7587C46}">
-  <dimension ref="A1:G1021"/>
+  <dimension ref="A1:G1022"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
@@ -29288,9 +29288,15 @@
       <c r="D1020" s="16" t="s">
         <v>1565</v>
       </c>
-      <c r="E1020" s="2"/>
-      <c r="F1020" s="2"/>
-      <c r="G1020" s="2"/>
+      <c r="E1020" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1020" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1020" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1021" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1021" s="1">
@@ -29299,15 +29305,44 @@
       <c r="B1021" s="7">
         <v>7501349029064</v>
       </c>
-      <c r="C1021" s="22">
+      <c r="C1021" s="16">
         <v>705</v>
       </c>
       <c r="D1021" s="16" t="s">
         <v>1577</v>
       </c>
-      <c r="E1021" s="2"/>
-      <c r="F1021" s="2"/>
-      <c r="G1021" s="2"/>
+      <c r="E1021" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1021" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1021" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1022" s="1">
+        <v>7502211783275</v>
+      </c>
+      <c r="B1022" s="12" t="s">
+        <v>996</v>
+      </c>
+      <c r="C1022" s="22">
+        <v>1000</v>
+      </c>
+      <c r="D1022" s="16" t="s">
+        <v>1695</v>
+      </c>
+      <c r="E1022" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1022" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1022" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/posiciones_buscador.xlsx
+++ b/posiciones_buscador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\desarrollos\buscador_posiciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB67A41-37E5-4BE2-BC94-0FC2CA744F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7762B751-3337-466F-8FC1-A145F938D120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81345FCE-0991-44B1-AB97-4BC767A118BC}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6132" uniqueCount="1718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6137" uniqueCount="1718">
   <si>
     <t>Cod. De Barras</t>
   </si>
@@ -5477,8 +5477,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G1022" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G1022" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G1023" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G1023" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G967">
     <sortCondition ref="C1:C967"/>
   </sortState>
@@ -5814,7 +5814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD76C0E-5FFA-48DF-BC8E-37CFF7587C46}">
-  <dimension ref="A1:G1022"/>
+  <dimension ref="A1:G1023"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
@@ -29328,7 +29328,7 @@
       <c r="B1022" s="12" t="s">
         <v>996</v>
       </c>
-      <c r="C1022" s="22">
+      <c r="C1022" s="16">
         <v>1000</v>
       </c>
       <c r="D1022" s="16" t="s">
@@ -29342,6 +29342,29 @@
       </c>
       <c r="G1022" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1023" s="20">
+        <v>7501349011984</v>
+      </c>
+      <c r="B1023" s="12" t="s">
+        <v>996</v>
+      </c>
+      <c r="C1023" s="22">
+        <v>714</v>
+      </c>
+      <c r="D1023" s="16" t="s">
+        <v>1579</v>
+      </c>
+      <c r="E1023" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1023" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1023" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/posiciones_buscador.xlsx
+++ b/posiciones_buscador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\desarrollos\buscador_posiciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7762B751-3337-466F-8FC1-A145F938D120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF2C950-563D-4AAC-9C5F-863AE90B468B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81345FCE-0991-44B1-AB97-4BC767A118BC}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6137" uniqueCount="1718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6142" uniqueCount="1719">
   <si>
     <t>Cod. De Barras</t>
   </si>
@@ -5198,6 +5198,9 @@
   </si>
   <si>
     <t>GEL DE SABILA REFRESCANTE 125 ML</t>
+  </si>
+  <si>
+    <t>FEMIREM TABLETAS C/60</t>
   </si>
 </sst>
 </file>
@@ -5477,8 +5480,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G1023" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G1023" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G1024" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G1024" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G967">
     <sortCondition ref="C1:C967"/>
   </sortState>
@@ -5814,7 +5817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD76C0E-5FFA-48DF-BC8E-37CFF7587C46}">
-  <dimension ref="A1:G1023"/>
+  <dimension ref="A1:G1024"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
@@ -29351,7 +29354,7 @@
       <c r="B1023" s="12" t="s">
         <v>996</v>
       </c>
-      <c r="C1023" s="22">
+      <c r="C1023" s="16">
         <v>714</v>
       </c>
       <c r="D1023" s="16" t="s">
@@ -29365,6 +29368,29 @@
       </c>
       <c r="G1023" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1024" s="1">
+        <v>7502009742736</v>
+      </c>
+      <c r="B1024" s="12" t="s">
+        <v>996</v>
+      </c>
+      <c r="C1024" s="22">
+        <v>99112</v>
+      </c>
+      <c r="D1024" s="16" t="s">
+        <v>1718</v>
+      </c>
+      <c r="E1024" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1024" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1024" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/posiciones_buscador.xlsx
+++ b/posiciones_buscador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\desarrollos\buscador_posiciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB43871-3FBA-4487-8D4D-B669A981AA19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898460BA-31DC-4330-B883-5F17DC82AD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81345FCE-0991-44B1-AB97-4BC767A118BC}"/>
   </bookViews>
@@ -18458,7 +18458,7 @@
         <v>759684432071</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>1430</v>
+        <v>993</v>
       </c>
       <c r="C550" s="2">
         <v>795</v>
@@ -19700,7 +19700,7 @@
         <v>759684154058</v>
       </c>
       <c r="B604" s="1" t="s">
-        <v>993</v>
+        <v>1430</v>
       </c>
       <c r="C604" s="2">
         <v>919</v>

--- a/posiciones_buscador.xlsx
+++ b/posiciones_buscador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\desarrollos\buscador_posiciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898460BA-31DC-4330-B883-5F17DC82AD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CC195A-8271-4AB5-81D5-10F4F6C9002B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81345FCE-0991-44B1-AB97-4BC767A118BC}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6142" uniqueCount="1717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="1717">
   <si>
     <t>Cod. De Barras</t>
   </si>
@@ -3181,9 +3181,6 @@
   </si>
   <si>
     <t>656599040103, 7501109763948</t>
-  </si>
-  <si>
-    <t>7501070635282, 7502006921967</t>
   </si>
   <si>
     <t>7501125190919, 7501349029828, 7503001007182, 780083144517</t>
@@ -5195,6 +5192,9 @@
   </si>
   <si>
     <t>SITAGLIPTINA 100 MG COMP C/28</t>
+  </si>
+  <si>
+    <t>QUINFAMIDA ALBENDAZOL SUSPENSION INFANTIL 100 ML</t>
   </si>
 </sst>
 </file>
@@ -5481,8 +5481,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G1024" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G1024" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G1025" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G1025" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G967">
     <sortCondition ref="C1:C967"/>
   </sortState>
@@ -5818,7 +5818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD76C0E-5FFA-48DF-BC8E-37CFF7587C46}">
-  <dimension ref="A1:G1024"/>
+  <dimension ref="A1:G1025"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
@@ -7187,8 +7187,8 @@
       <c r="A60" s="1">
         <v>7502006921974</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>1046</v>
+      <c r="B60" s="7">
+        <v>7501070635282</v>
       </c>
       <c r="C60" s="2">
         <v>80</v>
@@ -7211,7 +7211,7 @@
         <v>7502009740503</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C61" s="2">
         <v>81</v>
@@ -7234,7 +7234,7 @@
         <v>7502009740763</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C62" s="2">
         <v>82</v>
@@ -7257,7 +7257,7 @@
         <v>7501563380736</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C63" s="2">
         <v>83</v>
@@ -7280,7 +7280,7 @@
         <v>7502006920038</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C64" s="2">
         <v>84</v>
@@ -7303,7 +7303,7 @@
         <v>785118753757</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C65" s="2">
         <v>85</v>
@@ -7326,7 +7326,7 @@
         <v>7502009740497</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C66" s="2">
         <v>86</v>
@@ -7349,7 +7349,7 @@
         <v>7502240450230</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C67" s="2">
         <v>87</v>
@@ -7372,7 +7372,7 @@
         <v>785120754810</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="C68" s="2">
         <v>88</v>
@@ -7395,7 +7395,7 @@
         <v>7501075717860</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C69" s="2">
         <v>89</v>
@@ -7418,7 +7418,7 @@
         <v>7502211783527</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C70" s="2">
         <v>90</v>
@@ -7441,7 +7441,7 @@
         <v>7502003381672</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C71" s="2">
         <v>91</v>
@@ -7464,7 +7464,7 @@
         <v>7503003738404</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="C72" s="2">
         <v>92</v>
@@ -7487,7 +7487,7 @@
         <v>7502009745140</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C73" s="2">
         <v>93</v>
@@ -7510,7 +7510,7 @@
         <v>785118752521</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="C74" s="2">
         <v>94</v>
@@ -7533,7 +7533,7 @@
         <v>7501125106750</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C75" s="2">
         <v>95</v>
@@ -7556,7 +7556,7 @@
         <v>7502208892249</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="C76" s="2">
         <v>96</v>
@@ -7579,7 +7579,7 @@
         <v>7502208892256</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="C77" s="2">
         <v>97</v>
@@ -7602,7 +7602,7 @@
         <v>7501349025271</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="C78" s="2">
         <v>98</v>
@@ -7625,7 +7625,7 @@
         <v>7502009745485</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C79" s="2">
         <v>99</v>
@@ -7648,7 +7648,7 @@
         <v>7503002047101</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C80" s="2">
         <v>100</v>
@@ -7671,7 +7671,7 @@
         <v>7502009740916</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C81" s="2">
         <v>101</v>
@@ -7694,7 +7694,7 @@
         <v>7501752513204</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C82" s="2">
         <v>102</v>
@@ -7740,7 +7740,7 @@
         <v>7501075718546</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C84" s="2">
         <v>104</v>
@@ -7763,7 +7763,7 @@
         <v>759684901058</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C85" s="2">
         <v>105</v>
@@ -7786,7 +7786,7 @@
         <v>785118752705</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C86" s="2">
         <v>107</v>
@@ -7809,7 +7809,7 @@
         <v>780083148966</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C87" s="2">
         <v>108</v>
@@ -7832,7 +7832,7 @@
         <v>7501825301271</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C88" s="2">
         <v>109</v>
@@ -7855,7 +7855,7 @@
         <v>7502211781059</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="C89" s="2">
         <v>110</v>
@@ -7878,7 +7878,7 @@
         <v>7501349023468</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C90" s="2">
         <v>113</v>
@@ -7901,7 +7901,7 @@
         <v>7501573905677</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="C91" s="2">
         <v>114</v>
@@ -7924,7 +7924,7 @@
         <v>7501573900115</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C92" s="2">
         <v>115</v>
@@ -7947,7 +7947,7 @@
         <v>7501537102920</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C93" s="2">
         <v>116</v>
@@ -7970,7 +7970,7 @@
         <v>7501349024595</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C94" s="2">
         <v>117</v>
@@ -8039,7 +8039,7 @@
         <v>7502213049188</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C97" s="2">
         <v>120</v>
@@ -8062,7 +8062,7 @@
         <v>7502213048457</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C98" s="2">
         <v>121</v>
@@ -8085,7 +8085,7 @@
         <v>7501349029330</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C99" s="2">
         <v>122</v>
@@ -8108,7 +8108,7 @@
         <v>7502009745126</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C100" s="2">
         <v>127</v>
@@ -8131,7 +8131,7 @@
         <v>7502009746093</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="C101" s="2">
         <v>128</v>
@@ -8154,7 +8154,7 @@
         <v>7502216805361</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C102" s="2">
         <v>129</v>
@@ -8177,7 +8177,7 @@
         <v>7501349028043</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="C103" s="2">
         <v>130</v>
@@ -8223,7 +8223,7 @@
         <v>7502223112445</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C105" s="2">
         <v>133</v>
@@ -8338,7 +8338,7 @@
         <v>7501482201884</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="C110" s="2">
         <v>141</v>
@@ -8361,7 +8361,7 @@
         <v>7501384547400</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C111" s="2">
         <v>142</v>
@@ -8384,7 +8384,7 @@
         <v>7501075710724</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="C112" s="2">
         <v>143</v>
@@ -8407,7 +8407,7 @@
         <v>637420202600</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C113" s="2">
         <v>146</v>
@@ -8430,7 +8430,7 @@
         <v>780083142483</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C114" s="2">
         <v>149</v>
@@ -8453,7 +8453,7 @@
         <v>7502009741050</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C115" s="2">
         <v>150</v>
@@ -8499,7 +8499,7 @@
         <v>7502009741425</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="C117" s="2">
         <v>152</v>
@@ -8545,7 +8545,7 @@
         <v>7503000422627</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="C119" s="2">
         <v>156</v>
@@ -8568,7 +8568,7 @@
         <v>7502208891891</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="C120" s="2">
         <v>157</v>
@@ -8614,7 +8614,7 @@
         <v>7501349021150</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="C122" s="2">
         <v>160</v>
@@ -8637,7 +8637,7 @@
         <v>7502208894557</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="C123" s="2">
         <v>162</v>
@@ -8683,7 +8683,7 @@
         <v>7502208891235</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="C125" s="2">
         <v>164</v>
@@ -8752,7 +8752,7 @@
         <v>785120754254</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="C128" s="2">
         <v>167</v>
@@ -8775,7 +8775,7 @@
         <v>7501573900900</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C129" s="2">
         <v>168</v>
@@ -8798,7 +8798,7 @@
         <v>780083140540</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C130" s="2">
         <v>169</v>
@@ -8821,7 +8821,7 @@
         <v>780083144814</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="C131" s="2">
         <v>170</v>
@@ -8844,7 +8844,7 @@
         <v>7503000422184</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C132" s="2">
         <v>171</v>
@@ -8867,7 +8867,7 @@
         <v>7501573921479</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C133" s="2">
         <v>172</v>
@@ -8913,7 +8913,7 @@
         <v>7502009740510</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C135" s="2">
         <v>174</v>
@@ -8936,7 +8936,7 @@
         <v>785118752347</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="C136" s="2">
         <v>175</v>
@@ -8959,7 +8959,7 @@
         <v>7502009740558</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C137" s="2">
         <v>176</v>
@@ -8982,7 +8982,7 @@
         <v>7501349020023</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C138" s="2">
         <v>177</v>
@@ -9028,7 +9028,7 @@
         <v>7501258203586</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C140" s="2">
         <v>179</v>
@@ -9051,7 +9051,7 @@
         <v>7502003386141</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C141" s="2">
         <v>180</v>
@@ -9097,7 +9097,7 @@
         <v>7502004401805</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="C143" s="2">
         <v>183</v>
@@ -9120,7 +9120,7 @@
         <v>7501825300120</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="C144" s="2">
         <v>184</v>
@@ -9143,7 +9143,7 @@
         <v>7501573900153</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="C145" s="2">
         <v>185</v>
@@ -9166,7 +9166,7 @@
         <v>7501537102999</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C146" s="2">
         <v>186</v>
@@ -9189,7 +9189,7 @@
         <v>7502009741326</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C147" s="2">
         <v>187</v>
@@ -9212,7 +9212,7 @@
         <v>7501349021013</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C148" s="2">
         <v>188</v>
@@ -9235,7 +9235,7 @@
         <v>7501342805023</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C149" s="2">
         <v>189</v>
@@ -9258,7 +9258,7 @@
         <v>7501075713152</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C150" s="2">
         <v>190</v>
@@ -9281,7 +9281,7 @@
         <v>7502001164420</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C151" s="2">
         <v>191</v>
@@ -9304,7 +9304,7 @@
         <v>7502009740374</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="C152" s="2">
         <v>192</v>
@@ -9350,7 +9350,7 @@
         <v>7501573900351</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C154" s="2">
         <v>194</v>
@@ -9373,7 +9373,7 @@
         <v>7501537100452</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C155" s="2">
         <v>196</v>
@@ -9396,7 +9396,7 @@
         <v>7501537102180</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="C156" s="2">
         <v>198</v>
@@ -9419,7 +9419,7 @@
         <v>7501258205221</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="C157" s="2">
         <v>199</v>
@@ -9442,7 +9442,7 @@
         <v>7502227876428</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="C158" s="2">
         <v>200</v>
@@ -9465,7 +9465,7 @@
         <v>7501258210942</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="C159" s="2">
         <v>201</v>
@@ -9488,7 +9488,7 @@
         <v>7501258213547</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="C160" s="2">
         <v>202</v>
@@ -9511,7 +9511,7 @@
         <v>7502227425435</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="C161" s="2">
         <v>204</v>
@@ -9534,7 +9534,7 @@
         <v>785118752415</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="C162" s="2">
         <v>206</v>
@@ -9557,7 +9557,7 @@
         <v>7503003406174</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="C163" s="2">
         <v>207</v>
@@ -9580,7 +9580,7 @@
         <v>7503004908677</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C164" s="2">
         <v>208</v>
@@ -9603,7 +9603,7 @@
         <v>785118752330</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="C165" s="2">
         <v>210</v>
@@ -9626,7 +9626,7 @@
         <v>7502216797079</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="C166" s="2">
         <v>211</v>
@@ -9649,7 +9649,7 @@
         <v>7503002773147</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="C167" s="2">
         <v>212</v>
@@ -9718,7 +9718,7 @@
         <v>7502006920021</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="C170" s="2">
         <v>215</v>
@@ -9764,7 +9764,7 @@
         <v>7501258205870</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="C172" s="2">
         <v>217</v>
@@ -9787,7 +9787,7 @@
         <v>7501258205863</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="C173" s="2">
         <v>218</v>
@@ -9856,7 +9856,7 @@
         <v>7501075719260</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="C176" s="2">
         <v>222</v>
@@ -9879,7 +9879,7 @@
         <v>7501825300274</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="C177" s="2">
         <v>223</v>
@@ -9902,7 +9902,7 @@
         <v>7501825301004</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="C178" s="2">
         <v>224</v>
@@ -9925,7 +9925,7 @@
         <v>780083140274</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="C179" s="2">
         <v>225</v>
@@ -9948,7 +9948,7 @@
         <v>7502245840692</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C180" s="2">
         <v>227</v>
@@ -9971,7 +9971,7 @@
         <v>7502001162815</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="C181" s="2">
         <v>228</v>
@@ -9994,7 +9994,7 @@
         <v>780083139889</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="C182" s="2">
         <v>229</v>
@@ -10040,7 +10040,7 @@
         <v>7501537101961</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C184" s="2">
         <v>232</v>
@@ -10086,7 +10086,7 @@
         <v>7502216803862</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="C186" s="2">
         <v>234</v>
@@ -10132,7 +10132,7 @@
         <v>7502245840173</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="C188" s="2">
         <v>236</v>
@@ -10155,7 +10155,7 @@
         <v>780083141066</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="C189" s="2">
         <v>237</v>
@@ -10201,7 +10201,7 @@
         <v>7503001007090</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="C191" s="2">
         <v>242</v>
@@ -10247,7 +10247,7 @@
         <v>7501349017122</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="C193" s="2">
         <v>244</v>
@@ -10270,7 +10270,7 @@
         <v>7503001007106</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C194" s="2">
         <v>245</v>
@@ -10293,7 +10293,7 @@
         <v>7501563381733</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="C195" s="2">
         <v>246</v>
@@ -10316,7 +10316,7 @@
         <v>7501130713417</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="C196" s="2">
         <v>247</v>
@@ -10339,7 +10339,7 @@
         <v>7502001162549</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="C197" s="2">
         <v>248</v>
@@ -10362,7 +10362,7 @@
         <v>7501385491252</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="C198" s="2">
         <v>249</v>
@@ -10385,7 +10385,7 @@
         <v>780083141226</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C199" s="2">
         <v>250</v>
@@ -10454,7 +10454,7 @@
         <v>7501537102586</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C202" s="2">
         <v>255</v>
@@ -10477,7 +10477,7 @@
         <v>8400005816</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="C203" s="2">
         <v>256</v>
@@ -10500,7 +10500,7 @@
         <v>7502226291857</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C204" s="2">
         <v>257</v>
@@ -10546,7 +10546,7 @@
         <v>7501825301875</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="C206" s="2">
         <v>259</v>
@@ -10569,7 +10569,7 @@
         <v>7502003388107</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="C207" s="2">
         <v>260</v>
@@ -10592,7 +10592,7 @@
         <v>7502216790865</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="C208" s="2">
         <v>261</v>
@@ -10684,7 +10684,7 @@
         <v>7502009745560</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="C212" s="2">
         <v>265</v>
@@ -10707,7 +10707,7 @@
         <v>7502009745737</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="C213" s="2">
         <v>266</v>
@@ -10753,7 +10753,7 @@
         <v>7502009745898</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="C215" s="2">
         <v>268</v>
@@ -10776,7 +10776,7 @@
         <v>7502009745997</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C216" s="2">
         <v>269</v>
@@ -10799,7 +10799,7 @@
         <v>7500326931505</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="C217" s="2">
         <v>270</v>
@@ -10822,7 +10822,7 @@
         <v>7502216796782</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="C218" s="2">
         <v>271</v>
@@ -10845,7 +10845,7 @@
         <v>7502216792845</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="C219" s="2">
         <v>272</v>
@@ -10868,7 +10868,7 @@
         <v>7502009744938</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C220" s="2">
         <v>273</v>
@@ -10891,7 +10891,7 @@
         <v>7502227426449</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C221" s="2">
         <v>275</v>
@@ -10983,7 +10983,7 @@
         <v>7501711669485</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C225" s="2">
         <v>280</v>
@@ -11006,7 +11006,7 @@
         <v>7503003134268</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="C226" s="2">
         <v>281</v>
@@ -11029,7 +11029,7 @@
         <v>7502216804746</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C227" s="2">
         <v>282</v>
@@ -11052,7 +11052,7 @@
         <v>7502009742132</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C228" s="2">
         <v>283</v>
@@ -11098,7 +11098,7 @@
         <v>7502009742149</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="C230" s="2">
         <v>285</v>
@@ -11121,7 +11121,7 @@
         <v>7502009746130</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="C231" s="2">
         <v>286</v>
@@ -11144,7 +11144,7 @@
         <v>7502009745881</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C232" s="2">
         <v>290</v>
@@ -11167,7 +11167,7 @@
         <v>7501075723397</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="C233" s="2">
         <v>291</v>
@@ -11190,7 +11190,7 @@
         <v>7502009745768</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C234" s="2">
         <v>293</v>
@@ -11213,7 +11213,7 @@
         <v>656599040479</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C235" s="2">
         <v>295</v>
@@ -11236,7 +11236,7 @@
         <v>7501644790034</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C236" s="2">
         <v>296</v>
@@ -11305,7 +11305,7 @@
         <v>785118752477</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="C239" s="2">
         <v>302</v>
@@ -11328,7 +11328,7 @@
         <v>7501349017931</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C240" s="2">
         <v>304</v>
@@ -11351,7 +11351,7 @@
         <v>7501563381252</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C241" s="2">
         <v>305</v>
@@ -11397,7 +11397,7 @@
         <v>7502227872185</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C243" s="2">
         <v>308</v>
@@ -11420,7 +11420,7 @@
         <v>7501573900191</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C244" s="2">
         <v>310</v>
@@ -11443,7 +11443,7 @@
         <v>656599040493</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C245" s="2">
         <v>311</v>
@@ -11489,7 +11489,7 @@
         <v>7503004908240</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C247" s="2">
         <v>314</v>
@@ -11512,7 +11512,7 @@
         <v>7502004401201</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C248" s="2">
         <v>315</v>
@@ -11535,7 +11535,7 @@
         <v>7501075717563</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C249" s="2">
         <v>316</v>
@@ -11558,7 +11558,7 @@
         <v>7501048333103</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C250" s="2">
         <v>317</v>
@@ -11581,7 +11581,7 @@
         <v>7501563310337</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C251" s="2">
         <v>319</v>
@@ -11604,7 +11604,7 @@
         <v>7502001162013</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C252" s="2">
         <v>320</v>
@@ -11627,7 +11627,7 @@
         <v>7501573900375</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="C253" s="2">
         <v>322</v>
@@ -11673,7 +11673,7 @@
         <v>729513103915</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="C255" s="2">
         <v>337</v>
@@ -11719,7 +11719,7 @@
         <v>7500326108754</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C257" s="2">
         <v>340</v>
@@ -11742,7 +11742,7 @@
         <v>7502216804739</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C258" s="2">
         <v>344</v>
@@ -11765,7 +11765,7 @@
         <v>7502001161368</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="C259" s="2">
         <v>345</v>
@@ -11811,7 +11811,7 @@
         <v>7501075714739</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="C261" s="2">
         <v>351</v>
@@ -11834,7 +11834,7 @@
         <v>7502211784029</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C262" s="2">
         <v>352</v>
@@ -11857,7 +11857,7 @@
         <v>7503007662163</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C263" s="2">
         <v>353</v>
@@ -11880,7 +11880,7 @@
         <v>7501573904335</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="C264" s="2">
         <v>354</v>
@@ -11903,7 +11903,7 @@
         <v>7502231320313</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="C265" s="2">
         <v>356</v>
@@ -11926,7 +11926,7 @@
         <v>7502224240659</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="C266" s="2">
         <v>358</v>
@@ -11949,7 +11949,7 @@
         <v>7502211784036</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="C267" s="2">
         <v>361</v>
@@ -12041,7 +12041,7 @@
         <v>7501537182960</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="C271" s="2">
         <v>382</v>
@@ -12064,7 +12064,7 @@
         <v>7501752514119</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="C272" s="2">
         <v>384</v>
@@ -12087,7 +12087,7 @@
         <v>7503000422320</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C273" s="2">
         <v>387</v>
@@ -12110,7 +12110,7 @@
         <v>7502009746000</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="C274" s="2">
         <v>388</v>
@@ -12133,7 +12133,7 @@
         <v>7503000422337</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="C275" s="2">
         <v>389</v>
@@ -12156,7 +12156,7 @@
         <v>7501478315540</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="C276" s="2">
         <v>390</v>
@@ -12202,7 +12202,7 @@
         <v>7502001165014</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="C278" s="2">
         <v>392</v>
@@ -12225,7 +12225,7 @@
         <v>7501537194130</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C279" s="2">
         <v>393</v>
@@ -12271,7 +12271,7 @@
         <v>7501122901112</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="C281" s="2">
         <v>395</v>
@@ -12317,7 +12317,7 @@
         <v>7502209855113</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="C283" s="2">
         <v>397</v>
@@ -12340,7 +12340,7 @@
         <v>7502216794993</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C284" s="2">
         <v>399</v>
@@ -12363,7 +12363,7 @@
         <v>785118753696</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C285" s="2">
         <v>400</v>
@@ -12409,7 +12409,7 @@
         <v>7502216803183</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="C287" s="2">
         <v>403</v>
@@ -12432,7 +12432,7 @@
         <v>7502216799325</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="C288" s="2">
         <v>404</v>
@@ -12455,7 +12455,7 @@
         <v>7502216790889</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="C289" s="2">
         <v>405</v>
@@ -12478,7 +12478,7 @@
         <v>785120754681</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C290" s="2">
         <v>406</v>
@@ -12501,7 +12501,7 @@
         <v>7502224246156</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="C291" s="2">
         <v>407</v>
@@ -12524,7 +12524,7 @@
         <v>7502224246149</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="C292" s="2">
         <v>408</v>
@@ -12547,7 +12547,7 @@
         <v>7501048660964</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C293" s="2">
         <v>409</v>
@@ -12570,7 +12570,7 @@
         <v>7501048660520</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C294" s="2">
         <v>410</v>
@@ -12593,7 +12593,7 @@
         <v>7501048660582</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="C295" s="2">
         <v>411</v>
@@ -12616,7 +12616,7 @@
         <v>7502224246033</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="C296" s="2">
         <v>412</v>
@@ -12639,7 +12639,7 @@
         <v>7501048660490</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="C297" s="2">
         <v>413</v>
@@ -12662,7 +12662,7 @@
         <v>7502224246101</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="C298" s="2">
         <v>414</v>
@@ -12685,7 +12685,7 @@
         <v>7506022326737</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="C299" s="2">
         <v>415</v>
@@ -12754,7 +12754,7 @@
         <v>7501075713190</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="C302" s="2">
         <v>426</v>
@@ -12800,7 +12800,7 @@
         <v>7501573900528</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="C304" s="2">
         <v>430</v>
@@ -12823,7 +12823,7 @@
         <v>7502001165151</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="C305" s="2">
         <v>431</v>
@@ -12846,7 +12846,7 @@
         <v>7502216801196</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="C306" s="2">
         <v>433</v>
@@ -12869,7 +12869,7 @@
         <v>7501349024458</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="C307" s="2">
         <v>434</v>
@@ -12892,7 +12892,7 @@
         <v>7502211780229</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="C308" s="2">
         <v>435</v>
@@ -12915,7 +12915,7 @@
         <v>7502009740664</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="C309" s="2">
         <v>438</v>
@@ -12938,7 +12938,7 @@
         <v>7501258214469</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="C310" s="2">
         <v>440</v>
@@ -12961,7 +12961,7 @@
         <v>7502009740756</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="C311" s="2">
         <v>448</v>
@@ -12984,7 +12984,7 @@
         <v>7501573901105</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="C312" s="2">
         <v>449</v>
@@ -13007,7 +13007,7 @@
         <v>7502211784272</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C313" s="2">
         <v>450</v>
@@ -13076,7 +13076,7 @@
         <v>7501258205986</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="C316" s="2">
         <v>453</v>
@@ -13145,7 +13145,7 @@
         <v>7501573900283</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="C319" s="2">
         <v>457</v>
@@ -13168,7 +13168,7 @@
         <v>7502009740305</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="C320" s="2">
         <v>459</v>
@@ -13191,7 +13191,7 @@
         <v>780083141981</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="C321" s="2">
         <v>460</v>
@@ -13237,7 +13237,7 @@
         <v>7502213042066</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="C323" s="2">
         <v>462</v>
@@ -13260,7 +13260,7 @@
         <v>7501573925071</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C324" s="2">
         <v>464</v>
@@ -13283,7 +13283,7 @@
         <v>780083146214</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="C325" s="2">
         <v>465</v>
@@ -13306,7 +13306,7 @@
         <v>7502009740312</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="C326" s="2">
         <v>466</v>
@@ -13329,7 +13329,7 @@
         <v>7502009746239</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="C327" s="2">
         <v>467</v>
@@ -13352,7 +13352,7 @@
         <v>7502009740817</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="C328" s="2">
         <v>468</v>
@@ -13375,7 +13375,7 @@
         <v>7502009741784</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="C329" s="2">
         <v>469</v>
@@ -13398,7 +13398,7 @@
         <v>7502216795204</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="C330" s="2">
         <v>470</v>
@@ -13421,7 +13421,7 @@
         <v>7502240450070</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="C331" s="2">
         <v>471</v>
@@ -13444,7 +13444,7 @@
         <v>7501109763436</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="C332" s="2">
         <v>472</v>
@@ -13467,7 +13467,7 @@
         <v>7501384544003</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C333" s="2">
         <v>473</v>
@@ -13490,7 +13490,7 @@
         <v>7501075711615</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="C334" s="2">
         <v>477</v>
@@ -13536,7 +13536,7 @@
         <v>7502004403458</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="C336" s="2">
         <v>479</v>
@@ -13559,7 +13559,7 @@
         <v>7502001162525</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="C337" s="2">
         <v>480</v>
@@ -13628,7 +13628,7 @@
         <v>7501075723182</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C340" s="2">
         <v>483</v>
@@ -13651,7 +13651,7 @@
         <v>780083142285</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="C341" s="2">
         <v>484</v>
@@ -13674,7 +13674,7 @@
         <v>780083142292</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C342" s="2">
         <v>485</v>
@@ -13720,7 +13720,7 @@
         <v>7502211788928</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C344" s="2">
         <v>487</v>
@@ -13766,7 +13766,7 @@
         <v>7501349022430</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="C346" s="2">
         <v>490</v>
@@ -13789,7 +13789,7 @@
         <v>7502006923619</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="C347" s="2">
         <v>492</v>
@@ -13812,7 +13812,7 @@
         <v>7501075714135</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="C348" s="2">
         <v>493</v>
@@ -13835,7 +13835,7 @@
         <v>780083140076</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="C349" s="2">
         <v>494</v>
@@ -13858,7 +13858,7 @@
         <v>7501075717020</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="C350" s="2">
         <v>495</v>
@@ -13904,7 +13904,7 @@
         <v>7501573900252</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="C352" s="2">
         <v>497</v>
@@ -13927,7 +13927,7 @@
         <v>7501573900122</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="C353" s="2">
         <v>498</v>
@@ -13973,7 +13973,7 @@
         <v>75006433</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C355" s="2">
         <v>501</v>
@@ -13996,7 +13996,7 @@
         <v>7502208892638</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C356" s="2">
         <v>502</v>
@@ -14019,7 +14019,7 @@
         <v>7501075714173</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="C357" s="2">
         <v>503</v>
@@ -14042,7 +14042,7 @@
         <v>7502211788935</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="C358" s="2">
         <v>504</v>
@@ -14065,7 +14065,7 @@
         <v>7501075713176</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C359" s="2">
         <v>506</v>
@@ -14088,7 +14088,7 @@
         <v>7501075717044</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="C360" s="2">
         <v>508</v>
@@ -14111,7 +14111,7 @@
         <v>7502211780069</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="C361" s="2">
         <v>509</v>
@@ -14134,7 +14134,7 @@
         <v>7502211784289</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C362" s="2">
         <v>510</v>
@@ -14180,7 +14180,7 @@
         <v>7501075713183</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C364" s="2">
         <v>512</v>
@@ -14203,7 +14203,7 @@
         <v>7503004908714</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="C365" s="2">
         <v>513</v>
@@ -14226,7 +14226,7 @@
         <v>7502227874127</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="C366" s="2">
         <v>515</v>
@@ -14249,7 +14249,7 @@
         <v>7502216792197</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="C367" s="2">
         <v>516</v>
@@ -14295,7 +14295,7 @@
         <v>7501349024632</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C369" s="2">
         <v>518</v>
@@ -14318,7 +14318,7 @@
         <v>7501258207584</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="C370" s="2">
         <v>519</v>
@@ -14341,7 +14341,7 @@
         <v>7502216796843</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="C371" s="2">
         <v>520</v>
@@ -14364,7 +14364,7 @@
         <v>7502216796836</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C372" s="2">
         <v>521</v>
@@ -14387,7 +14387,7 @@
         <v>7502009745027</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="C373" s="2">
         <v>522</v>
@@ -14433,7 +14433,7 @@
         <v>7502009745522</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="C375" s="2">
         <v>524</v>
@@ -14479,7 +14479,7 @@
         <v>7502009744129</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="C377" s="2">
         <v>526</v>
@@ -14502,7 +14502,7 @@
         <v>7502009740794</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="C378" s="2">
         <v>527</v>
@@ -14525,7 +14525,7 @@
         <v>7502223555303</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="C379" s="2">
         <v>528</v>
@@ -14548,7 +14548,7 @@
         <v>785118752965</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C380" s="2">
         <v>529</v>
@@ -14571,7 +14571,7 @@
         <v>785118753801</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C381" s="2">
         <v>530</v>
@@ -14594,7 +14594,7 @@
         <v>7502003388008</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="C382" s="2">
         <v>531</v>
@@ -14617,7 +14617,7 @@
         <v>7501836003256</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="C383" s="2">
         <v>532</v>
@@ -14640,7 +14640,7 @@
         <v>780083141325</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="C384" s="2">
         <v>533</v>
@@ -14663,7 +14663,7 @@
         <v>7502213042059</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="C385" s="2">
         <v>534</v>
@@ -14686,7 +14686,7 @@
         <v>7502009745546</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="C386" s="2">
         <v>535</v>
@@ -14709,7 +14709,7 @@
         <v>780083144807</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="C387" s="2">
         <v>536</v>
@@ -14732,7 +14732,7 @@
         <v>7501573900467</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="C388" s="2">
         <v>537</v>
@@ -14755,7 +14755,7 @@
         <v>785120754483</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="C389" s="2">
         <v>538</v>
@@ -14778,7 +14778,7 @@
         <v>780083141561</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="C390" s="2">
         <v>542</v>
@@ -14801,7 +14801,7 @@
         <v>7501493860636</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="C391" s="2">
         <v>543</v>
@@ -14824,7 +14824,7 @@
         <v>7501825300731</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="C392" s="2">
         <v>544</v>
@@ -14847,7 +14847,7 @@
         <v>7501573900030</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="C393" s="2">
         <v>545</v>
@@ -14870,7 +14870,7 @@
         <v>7501573900047</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="C394" s="2">
         <v>546</v>
@@ -14893,7 +14893,7 @@
         <v>7501562820233</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="C395" s="2">
         <v>548</v>
@@ -14939,7 +14939,7 @@
         <v>7501563310399</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C397" s="2">
         <v>552</v>
@@ -14962,7 +14962,7 @@
         <v>7503000422467</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C398" s="2">
         <v>553</v>
@@ -14985,7 +14985,7 @@
         <v>785118753900</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="C399" s="2">
         <v>554</v>
@@ -15008,7 +15008,7 @@
         <v>7502211788539</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="C400" s="2">
         <v>555</v>
@@ -15054,7 +15054,7 @@
         <v>7501109760770</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="C402" s="2">
         <v>558</v>
@@ -15077,7 +15077,7 @@
         <v>7502009745409</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C403" s="2">
         <v>561</v>
@@ -15100,7 +15100,7 @@
         <v>7502009745393</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="C404" s="2">
         <v>562</v>
@@ -15123,7 +15123,7 @@
         <v>619114450191</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="C405" s="2">
         <v>563</v>
@@ -15146,7 +15146,7 @@
         <v>7502216792289</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="C406" s="2">
         <v>564</v>
@@ -15169,7 +15169,7 @@
         <v>7501075722253</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="C407" s="2">
         <v>565</v>
@@ -15215,7 +15215,7 @@
         <v>8400005830</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="C409" s="2">
         <v>570</v>
@@ -15238,7 +15238,7 @@
         <v>8901120011131</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="C410" s="2">
         <v>571</v>
@@ -15284,7 +15284,7 @@
         <v>785118753887</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="C412" s="2">
         <v>576</v>
@@ -15307,7 +15307,7 @@
         <v>7502216792685</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="C413" s="2">
         <v>578</v>
@@ -15330,7 +15330,7 @@
         <v>637420720326</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="C414" s="2">
         <v>579</v>
@@ -15353,7 +15353,7 @@
         <v>7502001163089</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="C415" s="2">
         <v>582</v>
@@ -15376,7 +15376,7 @@
         <v>7502222840776</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="C416" s="2">
         <v>583</v>
@@ -15399,7 +15399,7 @@
         <v>7502003385359</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="C417" s="2">
         <v>584</v>
@@ -15422,7 +15422,7 @@
         <v>7502223553477</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="C418" s="2">
         <v>585</v>
@@ -15445,7 +15445,7 @@
         <v>7502216792920</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="C419" s="2">
         <v>586</v>
@@ -15468,7 +15468,7 @@
         <v>7501075720501</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C420" s="2">
         <v>587</v>
@@ -15491,7 +15491,7 @@
         <v>780083144302</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="C421" s="2">
         <v>588</v>
@@ -15514,7 +15514,7 @@
         <v>780083144296</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="C422" s="2">
         <v>589</v>
@@ -15537,7 +15537,7 @@
         <v>7502009745317</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C423" s="2">
         <v>590</v>
@@ -15560,7 +15560,7 @@
         <v>7502216801691</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="C424" s="2">
         <v>591</v>
@@ -15583,7 +15583,7 @@
         <v>780083141936</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="C425" s="2">
         <v>592</v>
@@ -15606,7 +15606,7 @@
         <v>7501075718041</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="C426" s="2">
         <v>593</v>
@@ -15629,7 +15629,7 @@
         <v>7502226294131</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="C427" s="2">
         <v>594</v>
@@ -15652,7 +15652,7 @@
         <v>7502261160262</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="C428" s="2">
         <v>595</v>
@@ -15675,7 +15675,7 @@
         <v>7501188850072</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="C429" s="2">
         <v>596</v>
@@ -15698,7 +15698,7 @@
         <v>7502001165397</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="C430" s="2">
         <v>597</v>
@@ -15721,7 +15721,7 @@
         <v>7501573900443</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="C431" s="2">
         <v>598</v>
@@ -15744,7 +15744,7 @@
         <v>7501537168995</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="C432" s="2">
         <v>599</v>
@@ -15767,7 +15767,7 @@
         <v>7501836009746</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="C433" s="2">
         <v>600</v>
@@ -15790,7 +15790,7 @@
         <v>7502211788416</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="C434" s="2">
         <v>601</v>
@@ -15813,7 +15813,7 @@
         <v>7502211780045</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="C435" s="2">
         <v>602</v>
@@ -15836,7 +15836,7 @@
         <v>7501471888034</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="C436" s="2">
         <v>605</v>
@@ -15905,7 +15905,7 @@
         <v>7501573900498</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="C439" s="2">
         <v>608</v>
@@ -15928,7 +15928,7 @@
         <v>7502001165045</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C440" s="2">
         <v>609</v>
@@ -15951,7 +15951,7 @@
         <v>8400007018</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="C441" s="2">
         <v>610</v>
@@ -15997,7 +15997,7 @@
         <v>7502006922728</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="C443" s="2">
         <v>612</v>
@@ -16020,7 +16020,7 @@
         <v>7502216801646</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="C444" s="2">
         <v>613</v>
@@ -16043,7 +16043,7 @@
         <v>7502009745034</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="C445" s="2">
         <v>614</v>
@@ -16066,7 +16066,7 @@
         <v>780083142339</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="C446" s="2">
         <v>615</v>
@@ -16089,7 +16089,7 @@
         <v>7501537102395</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="C447" s="2">
         <v>616</v>
@@ -16112,7 +16112,7 @@
         <v>7502214983207</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C448" s="2">
         <v>620</v>
@@ -16135,7 +16135,7 @@
         <v>7501258203395</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C449" s="2">
         <v>621</v>
@@ -16181,7 +16181,7 @@
         <v>7502009742163</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="C451" s="2">
         <v>623</v>
@@ -16204,7 +16204,7 @@
         <v>7501075713770</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="C452" s="2">
         <v>624</v>
@@ -16227,7 +16227,7 @@
         <v>7501836009807</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="C453" s="2">
         <v>625</v>
@@ -16250,7 +16250,7 @@
         <v>759684391156</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="C454" s="2">
         <v>627</v>
@@ -16273,7 +16273,7 @@
         <v>7502214984358</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="C455" s="2">
         <v>628</v>
@@ -16296,7 +16296,7 @@
         <v>78008342827</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="C456" s="2">
         <v>630</v>
@@ -16319,7 +16319,7 @@
         <v>7501277031986</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="C457" s="2">
         <v>631</v>
@@ -16342,7 +16342,7 @@
         <v>7501109761388</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="C458" s="2">
         <v>637</v>
@@ -16365,7 +16365,7 @@
         <v>7501125155765</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C459" s="2">
         <v>643</v>
@@ -16411,7 +16411,7 @@
         <v>7502216799806</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="C461" s="2">
         <v>655</v>
@@ -16434,7 +16434,7 @@
         <v>7502216799813</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="C462" s="2">
         <v>656</v>
@@ -16457,7 +16457,7 @@
         <v>7502216799820</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="C463" s="2">
         <v>657</v>
@@ -16480,7 +16480,7 @@
         <v>7502009745379</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="C464" s="2">
         <v>658</v>
@@ -16503,7 +16503,7 @@
         <v>7501349024588</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="C465" s="2">
         <v>662</v>
@@ -16526,7 +16526,7 @@
         <v>7502261160057</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="C466" s="2">
         <v>668</v>
@@ -16595,7 +16595,7 @@
         <v>7501471887419</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="C469" s="2">
         <v>673</v>
@@ -16618,7 +16618,7 @@
         <v>7502227872192</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="C470" s="2">
         <v>674</v>
@@ -16687,7 +16687,7 @@
         <v>7501349012370</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="C473" s="2">
         <v>677</v>
@@ -16710,7 +16710,7 @@
         <v>7501836000828</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="C474" s="2">
         <v>678</v>
@@ -16733,7 +16733,7 @@
         <v>7501537102432</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="C475" s="2">
         <v>679</v>
@@ -16756,7 +16756,7 @@
         <v>670079000784</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="C476" s="2">
         <v>681</v>
@@ -16779,7 +16779,7 @@
         <v>7503003406242</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="C477" s="2">
         <v>683</v>
@@ -16848,7 +16848,7 @@
         <v>780083139759</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="C480" s="2">
         <v>687</v>
@@ -16871,7 +16871,7 @@
         <v>780083140212</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="C481" s="2">
         <v>688</v>
@@ -16894,7 +16894,7 @@
         <v>7502009746215</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="C482" s="2">
         <v>690</v>
@@ -16917,7 +16917,7 @@
         <v>7501349020962</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="C483" s="2">
         <v>692</v>
@@ -16940,7 +16940,7 @@
         <v>656599041216</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="C484" s="2">
         <v>693</v>
@@ -16963,7 +16963,7 @@
         <v>785118753788</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="C485" s="2">
         <v>694</v>
@@ -17032,7 +17032,7 @@
         <v>7503000422283</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="C488" s="2">
         <v>698</v>
@@ -17055,7 +17055,7 @@
         <v>7501075715095</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="C489" s="2">
         <v>699</v>
@@ -17078,7 +17078,7 @@
         <v>7501075715088</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="C490" s="2">
         <v>700</v>
@@ -17101,7 +17101,7 @@
         <v>7501547522145</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="C491" s="2">
         <v>701</v>
@@ -17147,7 +17147,7 @@
         <v>750200165441</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="C493" s="2">
         <v>704</v>
@@ -17170,7 +17170,7 @@
         <v>7501471888249</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="C494" s="2">
         <v>709</v>
@@ -17193,7 +17193,7 @@
         <v>7501258205078</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="C495" s="2">
         <v>710</v>
@@ -17216,7 +17216,7 @@
         <v>7502216798786</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="C496" s="2">
         <v>711</v>
@@ -17239,7 +17239,7 @@
         <v>7502211782483</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="C497" s="2">
         <v>712</v>
@@ -17262,7 +17262,7 @@
         <v>780083148423</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="C498" s="2">
         <v>713</v>
@@ -17308,7 +17308,7 @@
         <v>7502009744983</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="C500" s="2">
         <v>716</v>
@@ -17331,7 +17331,7 @@
         <v>780083143565</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="C501" s="2">
         <v>717</v>
@@ -17354,7 +17354,7 @@
         <v>7501075717686</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C502" s="2">
         <v>718</v>
@@ -17377,7 +17377,7 @@
         <v>7501349029170</v>
       </c>
       <c r="B503" s="1" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="C503" s="2">
         <v>719</v>
@@ -17400,7 +17400,7 @@
         <v>7502216808614</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="C504" s="2">
         <v>720</v>
@@ -17423,7 +17423,7 @@
         <v>7502216808645</v>
       </c>
       <c r="B505" s="1" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="C505" s="2">
         <v>721</v>
@@ -17446,7 +17446,7 @@
         <v>75049812</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="C506" s="2">
         <v>722</v>
@@ -17469,7 +17469,7 @@
         <v>7506022304452</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="C507" s="2">
         <v>723</v>
@@ -17515,7 +17515,7 @@
         <v>729513107890</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="C509" s="2">
         <v>727</v>
@@ -17538,7 +17538,7 @@
         <v>729513107944</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="C510" s="2">
         <v>728</v>
@@ -17561,7 +17561,7 @@
         <v>780083140731</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="C511" s="2">
         <v>729</v>
@@ -17584,7 +17584,7 @@
         <v>7501471889352</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="C512" s="2">
         <v>730</v>
@@ -17607,7 +17607,7 @@
         <v>729513107906</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="C513" s="2">
         <v>731</v>
@@ -17653,7 +17653,7 @@
         <v>7501289512633</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C515" s="2">
         <v>733</v>
@@ -17676,7 +17676,7 @@
         <v>7502004530079</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="C516" s="2">
         <v>734</v>
@@ -17699,7 +17699,7 @@
         <v>729513107883</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C517" s="2">
         <v>735</v>
@@ -17722,7 +17722,7 @@
         <v>7503002773161</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="C518" s="2">
         <v>737</v>
@@ -17745,7 +17745,7 @@
         <v>7501258206525</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C519" s="2">
         <v>739</v>
@@ -17768,7 +17768,7 @@
         <v>7501361111501</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="C520" s="2">
         <v>740</v>
@@ -17791,7 +17791,7 @@
         <v>7502216803916</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="C521" s="2">
         <v>742</v>
@@ -17814,7 +17814,7 @@
         <v>7702136645003</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="C522" s="2">
         <v>744</v>
@@ -17837,7 +17837,7 @@
         <v>736211494979</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="C523" s="2">
         <v>746</v>
@@ -17860,7 +17860,7 @@
         <v>785120754841</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="C524" s="2">
         <v>747</v>
@@ -17883,7 +17883,7 @@
         <v>785120755046</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="C525" s="2">
         <v>748</v>
@@ -17906,7 +17906,7 @@
         <v>785120755022</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="C526" s="2">
         <v>749</v>
@@ -17929,7 +17929,7 @@
         <v>7501349025806</v>
       </c>
       <c r="B527" s="1" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="C527" s="2">
         <v>751</v>
@@ -17952,7 +17952,7 @@
         <v>7501493888784</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="C528" s="2">
         <v>752</v>
@@ -17975,7 +17975,7 @@
         <v>7502216797369</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="C529" s="2">
         <v>753</v>
@@ -18021,7 +18021,7 @@
         <v>637420200897</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="C531" s="2">
         <v>758</v>
@@ -18044,7 +18044,7 @@
         <v>7501250882024</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="C532" s="2">
         <v>759</v>
@@ -18067,7 +18067,7 @@
         <v>7502009743986</v>
       </c>
       <c r="B533" s="1" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="C533" s="2">
         <v>766</v>
@@ -18090,7 +18090,7 @@
         <v>7502009747168</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="C534" s="2">
         <v>767</v>
@@ -18320,7 +18320,7 @@
         <v>729513100686</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="C544" s="2">
         <v>780</v>
@@ -18366,7 +18366,7 @@
         <v>759684155017</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="C546" s="2">
         <v>782</v>
@@ -18412,7 +18412,7 @@
         <v>759684351051</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C548" s="2">
         <v>789</v>
@@ -18435,7 +18435,7 @@
         <v>7503003406402</v>
       </c>
       <c r="B549" s="1" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C549" s="2">
         <v>794</v>
@@ -18481,7 +18481,7 @@
         <v>780083148843</v>
       </c>
       <c r="B551" s="1" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="C551" s="2">
         <v>800</v>
@@ -18504,7 +18504,7 @@
         <v>780083146955</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="C552" s="2">
         <v>803</v>
@@ -18527,7 +18527,7 @@
         <v>7501825305149</v>
       </c>
       <c r="B553" s="1" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="C553" s="2">
         <v>804</v>
@@ -18550,7 +18550,7 @@
         <v>7502009747373</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="C554" s="2">
         <v>811</v>
@@ -18619,7 +18619,7 @@
         <v>7502003389975</v>
       </c>
       <c r="B557" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="C557" s="2">
         <v>826</v>
@@ -18688,7 +18688,7 @@
         <v>7502268542207</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="C560" s="2">
         <v>831</v>
@@ -18734,7 +18734,7 @@
         <v>7502247373914</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="C562" s="2">
         <v>835</v>
@@ -19010,7 +19010,7 @@
         <v>759684900105</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="C574" s="2">
         <v>874</v>
@@ -19033,7 +19033,7 @@
         <v>759684311451</v>
       </c>
       <c r="B575" s="1" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="C575" s="2">
         <v>875</v>
@@ -19079,7 +19079,7 @@
         <v>7501590286223</v>
       </c>
       <c r="B577" s="1" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="C577" s="2">
         <v>878</v>
@@ -19125,7 +19125,7 @@
         <v>7501590284779</v>
       </c>
       <c r="B579" s="1" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="C579" s="2">
         <v>881</v>
@@ -19194,7 +19194,7 @@
         <v>773042188775</v>
       </c>
       <c r="B582" s="1" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="C582" s="2">
         <v>884</v>
@@ -19332,7 +19332,7 @@
         <v>0</v>
       </c>
       <c r="B588" s="1" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="C588" s="2">
         <v>893</v>
@@ -19355,7 +19355,7 @@
         <v>759684154034</v>
       </c>
       <c r="B589" s="1" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="C589" s="2">
         <v>902</v>
@@ -19378,7 +19378,7 @@
         <v>7501109763375</v>
       </c>
       <c r="B590" s="1" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C590" s="2">
         <v>903</v>
@@ -19401,7 +19401,7 @@
         <v>7502216791619</v>
       </c>
       <c r="B591" s="1" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="C591" s="2">
         <v>904</v>
@@ -19470,7 +19470,7 @@
         <v>7501349027060</v>
       </c>
       <c r="B594" s="1" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="C594" s="2">
         <v>907</v>
@@ -19493,7 +19493,7 @@
         <v>7501349025059</v>
       </c>
       <c r="B595" s="1" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="C595" s="2">
         <v>908</v>
@@ -19631,7 +19631,7 @@
         <v>7502227876398</v>
       </c>
       <c r="B601" s="1" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="C601" s="2">
         <v>914</v>
@@ -19700,7 +19700,7 @@
         <v>759684154058</v>
       </c>
       <c r="B604" s="1" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="C604" s="2">
         <v>919</v>
@@ -19792,7 +19792,7 @@
         <v>7502216790896</v>
       </c>
       <c r="B608" s="1" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="C608" s="2">
         <v>978</v>
@@ -19815,7 +19815,7 @@
         <v>821998000571</v>
       </c>
       <c r="B609" s="1" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="C609" s="2">
         <v>979</v>
@@ -20160,7 +20160,7 @@
         <v>5601332</v>
       </c>
       <c r="B624" s="1" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="C624" s="2">
         <v>1051</v>
@@ -20551,7 +20551,7 @@
         <v>7501349021624</v>
       </c>
       <c r="B641" s="1" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="C641" s="2">
         <v>1115</v>
@@ -20833,7 +20833,7 @@
         <v>99111</v>
       </c>
       <c r="D653" s="5" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="E653" s="5" t="s">
         <v>23</v>
@@ -21172,7 +21172,7 @@
         <v>714908107098</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="C668" s="2">
         <v>9002</v>
@@ -21241,7 +21241,7 @@
         <v>714908105483</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="C671" s="2">
         <v>9009</v>
@@ -21264,7 +21264,7 @@
         <v>7501258206723</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="C672" s="2">
         <v>9013</v>
@@ -21402,7 +21402,7 @@
         <v>7502214010415</v>
       </c>
       <c r="B678" s="1" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="C678" s="2">
         <v>9021</v>
@@ -21494,7 +21494,7 @@
         <v>7502214011054</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="C682" s="2">
         <v>9031</v>
@@ -21540,7 +21540,7 @@
         <v>7502214011030</v>
       </c>
       <c r="B684" s="1" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="C684" s="2">
         <v>9033</v>
@@ -21609,7 +21609,7 @@
         <v>7502214010347</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="C687" s="2">
         <v>9038</v>
@@ -21655,7 +21655,7 @@
         <v>75035000242</v>
       </c>
       <c r="B689" s="1" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="C689" s="2">
         <v>9051</v>
@@ -21678,7 +21678,7 @@
         <v>7502244010126</v>
       </c>
       <c r="B690" s="1" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="C690" s="2">
         <v>9054</v>
@@ -21793,7 +21793,7 @@
         <v>7503007662194</v>
       </c>
       <c r="B695" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="C695" s="2">
         <v>9069</v>
@@ -21816,7 +21816,7 @@
         <v>7503007662255</v>
       </c>
       <c r="B696" s="1" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="C696" s="2">
         <v>9070</v>
@@ -21885,7 +21885,7 @@
         <v>7502214011023</v>
       </c>
       <c r="B699" s="1" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="C699" s="2">
         <v>9078</v>
@@ -21977,7 +21977,7 @@
         <v>7502010840193</v>
       </c>
       <c r="B703" s="1" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="C703" s="2">
         <v>9086</v>
@@ -22000,7 +22000,7 @@
         <v>7503007202437</v>
       </c>
       <c r="B704" s="1" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="C704" s="2">
         <v>9089</v>
@@ -22092,7 +22092,7 @@
         <v>803288480669</v>
       </c>
       <c r="B708" s="1" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="C708" s="2">
         <v>9107</v>
@@ -22115,7 +22115,7 @@
         <v>714908100099</v>
       </c>
       <c r="B709" s="1" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="C709" s="2">
         <v>9108</v>
@@ -22207,7 +22207,7 @@
         <v>7502010840292</v>
       </c>
       <c r="B713" s="1" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="C713" s="2">
         <v>9120</v>
@@ -22253,7 +22253,7 @@
         <v>7501384504939</v>
       </c>
       <c r="B715" s="1" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="C715" s="2">
         <v>9137</v>
@@ -22276,7 +22276,7 @@
         <v>7501590283048</v>
       </c>
       <c r="B716" s="1" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="C716" s="2">
         <v>9138</v>
@@ -22345,7 +22345,7 @@
         <v>714908100518</v>
       </c>
       <c r="B719" s="1" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="C719" s="2">
         <v>9146</v>
@@ -22368,7 +22368,7 @@
         <v>7502009743993</v>
       </c>
       <c r="B720" s="1" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="C720" s="2">
         <v>9147</v>
@@ -22506,7 +22506,7 @@
         <v>7503181042881</v>
       </c>
       <c r="B726" s="1" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="C726" s="2">
         <v>9173</v>
@@ -22644,7 +22644,7 @@
         <v>7501075712223</v>
       </c>
       <c r="B732" s="1" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="C732" s="2">
         <v>9193</v>
@@ -22667,7 +22667,7 @@
         <v>7500326106972</v>
       </c>
       <c r="B733" s="1" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="C733" s="2">
         <v>9195</v>
@@ -22736,7 +22736,7 @@
         <v>7503008344150</v>
       </c>
       <c r="B736" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="C736" s="2">
         <v>9199</v>
@@ -22851,7 +22851,7 @@
         <v>7502259891376</v>
       </c>
       <c r="B741" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="C741" s="2">
         <v>9227</v>
@@ -22920,7 +22920,7 @@
         <v>7502259891079</v>
       </c>
       <c r="B744" s="1" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="C744" s="2">
         <v>9234</v>
@@ -23150,7 +23150,7 @@
         <v>714908100822</v>
       </c>
       <c r="B754" s="1" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="C754" s="2">
         <v>9291</v>
@@ -23242,7 +23242,7 @@
         <v>7503011998753</v>
       </c>
       <c r="B758" s="1" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="C758" s="2">
         <v>9305</v>
@@ -23265,7 +23265,7 @@
         <v>7503011998760</v>
       </c>
       <c r="B759" s="1" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="C759" s="2">
         <v>9306</v>
@@ -23288,7 +23288,7 @@
         <v>7503011998746</v>
       </c>
       <c r="B760" s="1" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="C760" s="2">
         <v>9307</v>
@@ -23334,7 +23334,7 @@
         <v>7503000812015</v>
       </c>
       <c r="B762" s="1" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="C762" s="2">
         <v>9325</v>
@@ -23449,7 +23449,7 @@
         <v>7500326106989</v>
       </c>
       <c r="B767" s="1" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="C767" s="2">
         <v>9341</v>
@@ -23472,7 +23472,7 @@
         <v>7500326108747</v>
       </c>
       <c r="B768" s="1" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="C768" s="2">
         <v>9343</v>
@@ -23610,7 +23610,7 @@
         <v>803288480218</v>
       </c>
       <c r="B774" s="1" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="C774" s="2">
         <v>9363</v>
@@ -23633,7 +23633,7 @@
         <v>803288480737</v>
       </c>
       <c r="B775" s="1" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="C775" s="2">
         <v>9385</v>
@@ -23702,7 +23702,7 @@
         <v>7501130704231</v>
       </c>
       <c r="B778" s="1" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="C778" s="2">
         <v>9447</v>
@@ -24024,7 +24024,7 @@
         <v>631758002192</v>
       </c>
       <c r="B792" s="1" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="C792" s="2">
         <v>9500</v>
@@ -24047,7 +24047,7 @@
         <v>750350000402</v>
       </c>
       <c r="B793" s="1" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="C793" s="2">
         <v>9505</v>
@@ -24254,7 +24254,7 @@
         <v>7502001165489</v>
       </c>
       <c r="B802" s="1" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="C802" s="2">
         <v>9594</v>
@@ -24277,7 +24277,7 @@
         <v>7501590284335</v>
       </c>
       <c r="B803" s="1" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="C803" s="2">
         <v>9622</v>
@@ -24300,7 +24300,7 @@
         <v>7500462199586</v>
       </c>
       <c r="B804" s="1" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="C804" s="2">
         <v>9632</v>
@@ -24323,7 +24323,7 @@
         <v>7500462199685</v>
       </c>
       <c r="B805" s="1" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="C805" s="2">
         <v>9633</v>
@@ -24346,7 +24346,7 @@
         <v>7500462199692</v>
       </c>
       <c r="B806" s="1" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="C806" s="2">
         <v>9634</v>
@@ -24438,7 +24438,7 @@
         <v>750104003574</v>
       </c>
       <c r="B810" s="1" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="C810" s="2">
         <v>9704</v>
@@ -24461,7 +24461,7 @@
         <v>750104003574</v>
       </c>
       <c r="B811" s="1" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="C811" s="2">
         <v>9704</v>
@@ -24484,7 +24484,7 @@
         <v>7502275940065</v>
       </c>
       <c r="B812" s="1" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="C812" s="2">
         <v>9705</v>
@@ -24507,7 +24507,7 @@
         <v>750104002027</v>
       </c>
       <c r="B813" s="1" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="C813" s="2">
         <v>9707</v>
@@ -24530,7 +24530,7 @@
         <v>750104003314</v>
       </c>
       <c r="B814" s="1" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="C814" s="2">
         <v>9709</v>
@@ -24576,7 +24576,7 @@
         <v>7502007700226</v>
       </c>
       <c r="B816" s="1" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="C816" s="2">
         <v>9715</v>
@@ -24599,7 +24599,7 @@
         <v>7502007700271</v>
       </c>
       <c r="B817" s="1" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="C817" s="2">
         <v>9716</v>
@@ -24668,7 +24668,7 @@
         <v>714908105957</v>
       </c>
       <c r="B820" s="1" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="C820" s="2">
         <v>9731</v>
@@ -24691,7 +24691,7 @@
         <v>7501172018228</v>
       </c>
       <c r="B821" s="1" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="C821" s="2">
         <v>9733</v>
@@ -24760,7 +24760,7 @@
         <v>7501825300885</v>
       </c>
       <c r="B824" s="1" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="C824" s="2">
         <v>9737</v>
@@ -24783,7 +24783,7 @@
         <v>7503008344617</v>
       </c>
       <c r="B825" s="1" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="C825" s="2">
         <v>9738</v>
@@ -24806,7 +24806,7 @@
         <v>7503002047620</v>
       </c>
       <c r="B826" s="1" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="C826" s="2">
         <v>9739</v>
@@ -24852,7 +24852,7 @@
         <v>7502010840360</v>
       </c>
       <c r="B828" s="1" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="C828" s="2">
         <v>9745</v>
@@ -24875,7 +24875,7 @@
         <v>7501060808016</v>
       </c>
       <c r="B829" s="1" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="C829" s="2">
         <v>9747</v>
@@ -24967,7 +24967,7 @@
         <v>7502001164338</v>
       </c>
       <c r="B833" s="1" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="C833" s="2">
         <v>9771</v>
@@ -25036,7 +25036,7 @@
         <v>7501258207010</v>
       </c>
       <c r="B836" s="1" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="C836" s="2">
         <v>9780</v>
@@ -25082,7 +25082,7 @@
         <v>7502280810605</v>
       </c>
       <c r="B838" s="1" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="C838" s="2">
         <v>9782</v>
@@ -25105,7 +25105,7 @@
         <v>7502280810056</v>
       </c>
       <c r="B839" s="1" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="C839" s="2">
         <v>9783</v>
@@ -25404,7 +25404,7 @@
         <v>7502314550002</v>
       </c>
       <c r="B852" s="1" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="C852" s="2">
         <v>9822</v>
@@ -25450,7 +25450,7 @@
         <v>7502227421666</v>
       </c>
       <c r="B854" s="1" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="C854" s="2">
         <v>9842</v>
@@ -25473,7 +25473,7 @@
         <v>7500462933746</v>
       </c>
       <c r="B855" s="1" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="C855" s="2">
         <v>9843</v>
@@ -25611,7 +25611,7 @@
         <v>7506021101564</v>
       </c>
       <c r="B861" s="1" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="C861" s="2">
         <v>9849</v>
@@ -25657,7 +25657,7 @@
         <v>7501130711642</v>
       </c>
       <c r="B863" s="1" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="C863" s="2">
         <v>9854</v>
@@ -25703,7 +25703,7 @@
         <v>750113071868</v>
       </c>
       <c r="B865" s="1" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="C865" s="2">
         <v>9856</v>
@@ -25726,7 +25726,7 @@
         <v>7506021100710</v>
       </c>
       <c r="B866" s="1" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="C866" s="2">
         <v>9858</v>
@@ -25818,7 +25818,7 @@
         <v>7506504900592</v>
       </c>
       <c r="B870" s="1" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="C870" s="2">
         <v>9865</v>
@@ -25841,7 +25841,7 @@
         <v>7502214018350</v>
       </c>
       <c r="B871" s="1" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="C871" s="2">
         <v>9866</v>
@@ -26232,7 +26232,7 @@
         <v>759684191077</v>
       </c>
       <c r="B888" s="1" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="C888" s="2">
         <v>9883</v>
@@ -26761,7 +26761,7 @@
         <v>7502259892250</v>
       </c>
       <c r="B911" s="1" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="C911" s="2">
         <v>9915</v>
@@ -27060,7 +27060,7 @@
         <v>731416423427</v>
       </c>
       <c r="B924" s="1" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="C924" s="2">
         <v>9928</v>
@@ -27319,7 +27319,7 @@
         <v>1155</v>
       </c>
       <c r="D935" s="2" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="E935" s="2" t="s">
         <v>21</v>
@@ -27549,7 +27549,7 @@
         <v>1150</v>
       </c>
       <c r="D945" s="2" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="E945" s="2" t="s">
         <v>23</v>
@@ -27572,7 +27572,7 @@
         <v>1152</v>
       </c>
       <c r="D946" s="2" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="E946" s="2" t="s">
         <v>23</v>
@@ -27595,7 +27595,7 @@
         <v>1151</v>
       </c>
       <c r="D947" s="2" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="E947" s="2" t="s">
         <v>23</v>
@@ -27635,7 +27635,7 @@
         <v>677144634059</v>
       </c>
       <c r="B949" s="1" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="C949" s="2">
         <v>9970</v>
@@ -27658,7 +27658,7 @@
         <v>731416423427</v>
       </c>
       <c r="B950" s="1" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="C950" s="2">
         <v>9971</v>
@@ -28078,7 +28078,7 @@
         <v>1143</v>
       </c>
       <c r="D968" s="2" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="E968" s="13" t="s">
         <v>23</v>
@@ -28101,7 +28101,7 @@
         <v>9990</v>
       </c>
       <c r="D969" s="16" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="E969" s="2" t="s">
         <v>23</v>
@@ -28124,7 +28124,7 @@
         <v>9991</v>
       </c>
       <c r="D970" s="16" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="E970" s="2" t="s">
         <v>23</v>
@@ -28147,7 +28147,7 @@
         <v>9794</v>
       </c>
       <c r="D971" s="16" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="E971" s="2" t="s">
         <v>23</v>
@@ -28170,7 +28170,7 @@
         <v>9992</v>
       </c>
       <c r="D972" s="16" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="E972" s="2" t="s">
         <v>23</v>
@@ -28193,7 +28193,7 @@
         <v>9993</v>
       </c>
       <c r="D973" s="16" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="E973" s="2" t="s">
         <v>23</v>
@@ -28216,7 +28216,7 @@
         <v>9994</v>
       </c>
       <c r="D974" s="16" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="E974" s="2" t="s">
         <v>23</v>
@@ -28239,7 +28239,7 @@
         <v>9995</v>
       </c>
       <c r="D975" s="16" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="E975" s="2" t="s">
         <v>23</v>
@@ -28262,7 +28262,7 @@
         <v>9725</v>
       </c>
       <c r="D976" s="16" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="E976" s="2" t="s">
         <v>22</v>
@@ -28285,7 +28285,7 @@
         <v>1146</v>
       </c>
       <c r="D977" s="16" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="E977" s="2" t="s">
         <v>21</v>
@@ -28308,7 +28308,7 @@
         <v>9725</v>
       </c>
       <c r="D978" s="16" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="E978" t="s">
         <v>22</v>
@@ -28331,7 +28331,7 @@
         <v>626</v>
       </c>
       <c r="D979" s="16" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="E979" t="s">
         <v>23</v>
@@ -28354,7 +28354,7 @@
         <v>9728</v>
       </c>
       <c r="D980" s="16" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="E980" t="s">
         <v>22</v>
@@ -28377,7 +28377,7 @@
         <v>9708</v>
       </c>
       <c r="D981" s="16" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="E981" t="s">
         <v>22</v>
@@ -28400,7 +28400,7 @@
         <v>9710</v>
       </c>
       <c r="D982" s="16" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="E982" t="s">
         <v>22</v>
@@ -28423,7 +28423,7 @@
         <v>9998</v>
       </c>
       <c r="D983" s="16" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="E983" t="s">
         <v>23</v>
@@ -28446,7 +28446,7 @@
         <v>9996</v>
       </c>
       <c r="D984" s="16" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="E984" t="s">
         <v>23</v>
@@ -28469,7 +28469,7 @@
         <v>9999</v>
       </c>
       <c r="D985" s="16" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="E985" t="s">
         <v>23</v>
@@ -28492,7 +28492,7 @@
         <v>99100</v>
       </c>
       <c r="D986" s="16" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="E986" t="s">
         <v>23</v>
@@ -28515,7 +28515,7 @@
         <v>9997</v>
       </c>
       <c r="D987" s="16" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="E987" t="s">
         <v>22</v>
@@ -28538,7 +28538,7 @@
         <v>99101</v>
       </c>
       <c r="D988" s="16" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="E988" t="s">
         <v>22</v>
@@ -28561,7 +28561,7 @@
         <v>1147</v>
       </c>
       <c r="D989" s="16" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="E989" s="2" t="s">
         <v>20</v>
@@ -28584,7 +28584,7 @@
         <v>1148</v>
       </c>
       <c r="D990" s="16" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="E990" s="2" t="s">
         <v>20</v>
@@ -28607,7 +28607,7 @@
         <v>9890</v>
       </c>
       <c r="D991" s="16" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="E991" s="2" t="s">
         <v>21</v>
@@ -28630,7 +28630,7 @@
         <v>9347</v>
       </c>
       <c r="D992" s="16" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="E992" s="2" t="s">
         <v>23</v>
@@ -28653,7 +28653,7 @@
         <v>901</v>
       </c>
       <c r="D993" s="16" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="E993" s="2" t="s">
         <v>23</v>
@@ -28670,13 +28670,13 @@
         <v>7502009742088</v>
       </c>
       <c r="B994" s="7" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="C994" s="16">
         <v>9023</v>
       </c>
       <c r="D994" s="16" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="E994" s="2" t="s">
         <v>23</v>
@@ -28699,7 +28699,7 @@
         <v>876</v>
       </c>
       <c r="D995" s="16" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="E995" s="2" t="s">
         <v>23</v>
@@ -28722,7 +28722,7 @@
         <v>976</v>
       </c>
       <c r="D996" s="16" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="E996" s="2" t="s">
         <v>23</v>
@@ -28745,7 +28745,7 @@
         <v>977</v>
       </c>
       <c r="D997" s="16" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="E997" s="2" t="s">
         <v>23</v>
@@ -28768,7 +28768,7 @@
         <v>418</v>
       </c>
       <c r="D998" s="16" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="E998" s="2" t="s">
         <v>23</v>
@@ -28791,7 +28791,7 @@
         <v>11101</v>
       </c>
       <c r="D999" s="16" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="E999" s="2" t="s">
         <v>22</v>
@@ -28814,7 +28814,7 @@
         <v>476</v>
       </c>
       <c r="D1000" s="16" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="E1000" t="s">
         <v>19</v>
@@ -28837,7 +28837,7 @@
         <v>9478</v>
       </c>
       <c r="D1001" s="16" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="E1001" t="s">
         <v>22</v>
@@ -28860,7 +28860,7 @@
         <v>1149</v>
       </c>
       <c r="D1002" s="16" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="E1002" t="s">
         <v>19</v>
@@ -28905,9 +28905,8 @@
       <c r="C1004" s="16">
         <v>182</v>
       </c>
-      <c r="D1004" s="16" t="str">
-        <f>VLOOKUP(Tabla13[[#This Row],[Codigo]],Hoja1!A2:C1005,3,0)</f>
-        <v>TRIMEBUTINA,SIMETICONA 200 MG C/24</v>
+      <c r="D1004" s="16" t="s">
+        <v>1696</v>
       </c>
       <c r="E1004" s="2" t="s">
         <v>21</v>
@@ -28929,9 +28928,8 @@
       <c r="C1005" s="16">
         <v>1137</v>
       </c>
-      <c r="D1005" s="16" t="str">
-        <f>VLOOKUP(Tabla13[[#This Row],[Codigo]],Hoja1!A3:C1006,3,0)</f>
-        <v>HIDRA2GO MORA AZUL</v>
+      <c r="D1005" s="16" t="s">
+        <v>1556</v>
       </c>
       <c r="E1005" s="2" t="s">
         <v>23</v>
@@ -28953,9 +28951,8 @@
       <c r="C1006" s="16">
         <v>1138</v>
       </c>
-      <c r="D1006" s="16" t="str">
-        <f>VLOOKUP(Tabla13[[#This Row],[Codigo]],Hoja1!A4:C1007,3,0)</f>
-        <v>HIDRA2GO FRESA-KIWI</v>
+      <c r="D1006" s="16" t="s">
+        <v>1557</v>
       </c>
       <c r="E1006" s="2" t="s">
         <v>23</v>
@@ -28977,9 +28974,8 @@
       <c r="C1007" s="16">
         <v>1139</v>
       </c>
-      <c r="D1007" s="16" t="str">
-        <f>VLOOKUP(Tabla13[[#This Row],[Codigo]],Hoja1!A5:C1008,3,0)</f>
-        <v>HIDRA2GO UVA</v>
+      <c r="D1007" s="16" t="s">
+        <v>1558</v>
       </c>
       <c r="E1007" s="2" t="s">
         <v>23</v>
@@ -29001,9 +28997,8 @@
       <c r="C1008" s="16">
         <v>1153</v>
       </c>
-      <c r="D1008" s="16" t="str">
-        <f>VLOOKUP(Tabla13[[#This Row],[Codigo]],Hoja1!A6:C1009,3,0)</f>
-        <v xml:space="preserve">PRE AFTER PARTY TABLETAS MASTICABLES </v>
+      <c r="D1008" s="16" t="s">
+        <v>1695</v>
       </c>
       <c r="E1008" s="2" t="s">
         <v>23</v>
@@ -29025,9 +29020,8 @@
       <c r="C1009" s="16">
         <v>9010</v>
       </c>
-      <c r="D1009" s="16" t="str">
-        <f>VLOOKUP(Tabla13[[#This Row],[Codigo]],Hoja1!A7:C1010,3,0)</f>
-        <v xml:space="preserve"> CLOROFILA  UB BOTE 500ML</v>
+      <c r="D1009" s="16" t="s">
+        <v>1578</v>
       </c>
       <c r="E1009" s="2" t="s">
         <v>23</v>
@@ -29049,9 +29043,8 @@
       <c r="C1010" s="16">
         <v>9730</v>
       </c>
-      <c r="D1010" s="16" t="str">
-        <f>VLOOKUP(Tabla13[[#This Row],[Codigo]],Hoja1!A8:C1011,3,0)</f>
-        <v>URBA CALÉNDULA CREMA FACIAL Y CORPORAL</v>
+      <c r="D1010" s="16" t="s">
+        <v>1597</v>
       </c>
       <c r="E1010" s="2" t="s">
         <v>23</v>
@@ -29073,9 +29066,8 @@
       <c r="C1011" s="16">
         <v>99102</v>
       </c>
-      <c r="D1011" s="16" t="str">
-        <f>VLOOKUP(Tabla13[[#This Row],[Codigo]],Hoja1!A9:C1012,3,0)</f>
-        <v>5 HTP</v>
+      <c r="D1011" s="16" t="s">
+        <v>1699</v>
       </c>
       <c r="E1011" s="2" t="s">
         <v>23</v>
@@ -29097,9 +29089,8 @@
       <c r="C1012" s="16">
         <v>99103</v>
       </c>
-      <c r="D1012" s="16" t="str">
-        <f>VLOOKUP(Tabla13[[#This Row],[Codigo]],Hoja1!A10:C1013,3,0)</f>
-        <v>QUANTUM KIDS</v>
+      <c r="D1012" s="16" t="s">
+        <v>1700</v>
       </c>
       <c r="E1012" s="2" t="s">
         <v>23</v>
@@ -29121,9 +29112,8 @@
       <c r="C1013" s="16">
         <v>99104</v>
       </c>
-      <c r="D1013" s="16" t="str">
-        <f>VLOOKUP(Tabla13[[#This Row],[Codigo]],Hoja1!A11:C1014,3,0)</f>
-        <v xml:space="preserve">OSTEOVITAL </v>
+      <c r="D1013" s="16" t="s">
+        <v>1701</v>
       </c>
       <c r="E1013" s="2" t="s">
         <v>23</v>
@@ -29145,9 +29135,8 @@
       <c r="C1014" s="16">
         <v>99105</v>
       </c>
-      <c r="D1014" s="16" t="str">
-        <f>VLOOKUP(Tabla13[[#This Row],[Codigo]],Hoja1!A12:C1015,3,0)</f>
-        <v>TRIPLE MAGNESIO</v>
+      <c r="D1014" s="16" t="s">
+        <v>1702</v>
       </c>
       <c r="E1014" s="2" t="s">
         <v>23</v>
@@ -29169,9 +29158,8 @@
       <c r="C1015" s="16">
         <v>99106</v>
       </c>
-      <c r="D1015" s="16" t="str">
-        <f>VLOOKUP(Tabla13[[#This Row],[Codigo]],Hoja1!A13:C1016,3,0)</f>
-        <v>AJOLOTIUS MENTA -EUCALIPTO C/10</v>
+      <c r="D1015" s="16" t="s">
+        <v>1703</v>
       </c>
       <c r="E1015" s="2" t="s">
         <v>23</v>
@@ -29193,9 +29181,8 @@
       <c r="C1016" s="16">
         <v>99107</v>
       </c>
-      <c r="D1016" s="16" t="str">
-        <f>VLOOKUP(Tabla13[[#This Row],[Codigo]],Hoja1!A14:C1017,3,0)</f>
-        <v>VINAGRE DE MANZANA CON MIEL DE ABEJA 250 ML</v>
+      <c r="D1016" s="16" t="s">
+        <v>1704</v>
       </c>
       <c r="E1016" s="2" t="s">
         <v>23</v>
@@ -29217,9 +29204,8 @@
       <c r="C1017" s="16">
         <v>99108</v>
       </c>
-      <c r="D1017" s="16" t="str">
-        <f>VLOOKUP(Tabla13[[#This Row],[Codigo]],Hoja1!A15:C1018,3,0)</f>
-        <v>VINAGRE SIDRA DE MANZANA  DE 250 ML</v>
+      <c r="D1017" s="16" t="s">
+        <v>1705</v>
       </c>
       <c r="E1017" s="2" t="s">
         <v>23</v>
@@ -29241,9 +29227,8 @@
       <c r="C1018" s="16">
         <v>99109</v>
       </c>
-      <c r="D1018" s="16" t="str">
-        <f>VLOOKUP(Tabla13[[#This Row],[Codigo]],Hoja1!A16:C1019,3,0)</f>
-        <v>HNATURAL ASHWAGANDHA C/60 CAP.</v>
+      <c r="D1018" s="16" t="s">
+        <v>1706</v>
       </c>
       <c r="E1018" s="2" t="s">
         <v>23</v>
@@ -29265,9 +29250,8 @@
       <c r="C1019" s="16">
         <v>99110</v>
       </c>
-      <c r="D1019" s="16" t="str">
-        <f>VLOOKUP(Tabla13[[#This Row],[Codigo]],Hoja1!A17:C1020,3,0)</f>
-        <v>HNATURAL BERBERINA C/60 CPS</v>
+      <c r="D1019" s="16" t="s">
+        <v>1707</v>
       </c>
       <c r="E1019" s="2" t="s">
         <v>22</v>
@@ -29284,13 +29268,13 @@
         <v>7501349022515</v>
       </c>
       <c r="B1020" s="1" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="C1020" s="16">
         <v>158</v>
       </c>
       <c r="D1020" s="16" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="E1020" s="2" t="s">
         <v>19</v>
@@ -29313,7 +29297,7 @@
         <v>705</v>
       </c>
       <c r="D1021" s="16" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="E1021" s="2" t="s">
         <v>31</v>
@@ -29336,7 +29320,7 @@
         <v>1000</v>
       </c>
       <c r="D1022" s="16" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="E1022" t="s">
         <v>18</v>
@@ -29359,7 +29343,7 @@
         <v>714</v>
       </c>
       <c r="D1023" s="16" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="E1023" t="s">
         <v>31</v>
@@ -29378,11 +29362,11 @@
       <c r="B1024" s="12" t="s">
         <v>993</v>
       </c>
-      <c r="C1024" s="22">
+      <c r="C1024" s="16">
         <v>99112</v>
       </c>
       <c r="D1024" s="16" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="E1024" s="2" t="s">
         <v>23</v>
@@ -29391,13 +29375,36 @@
         <v>28</v>
       </c>
       <c r="G1024" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1025" s="20">
+        <v>7502006921967</v>
+      </c>
+      <c r="B1025" s="12" t="s">
+        <v>993</v>
+      </c>
+      <c r="C1025" s="22">
+        <v>1156</v>
+      </c>
+      <c r="D1025" s="16" t="s">
+        <v>1716</v>
+      </c>
+      <c r="E1025" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1025" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1025" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="D2:D652 D1002:D1003 D654:D934 D946 D935:D944 D947:D1001" calculatedColumn="1"/>
+    <ignoredError sqref="D2:D652 D1002:D1003 D654:D934 D946 D935:D944 D947:D1001 D1025 D1004:D1024" calculatedColumn="1"/>
     <ignoredError sqref="B949:B950" numberStoredAsText="1"/>
   </ignoredErrors>
   <tableParts count="1">
@@ -29413,13 +29420,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="23" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B1" s="24" t="s">
         <v>1550</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>1551</v>
-      </c>
-      <c r="C1" s="25" t="s">
-        <v>1552</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -30728,7 +30735,7 @@
         <v>81</v>
       </c>
       <c r="C120" s="29" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
@@ -30981,7 +30988,7 @@
         <v>24</v>
       </c>
       <c r="C143" s="29" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
@@ -31850,7 +31857,7 @@
         <v>0</v>
       </c>
       <c r="C222" s="29" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
@@ -31883,7 +31890,7 @@
         <v>5</v>
       </c>
       <c r="C225" s="27" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
@@ -31938,7 +31945,7 @@
         <v>4</v>
       </c>
       <c r="C230" s="27" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
@@ -31960,7 +31967,7 @@
         <v>0</v>
       </c>
       <c r="C232" s="27" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.35">
@@ -32730,7 +32737,7 @@
         <v>8</v>
       </c>
       <c r="C302" s="29" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.35">
@@ -32807,7 +32814,7 @@
         <v>0</v>
       </c>
       <c r="C309" s="27" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.35">
@@ -32851,7 +32858,7 @@
         <v>0</v>
       </c>
       <c r="C313" s="27" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.35">
@@ -33137,7 +33144,7 @@
         <v>0</v>
       </c>
       <c r="C339" s="29" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.35">
@@ -33764,7 +33771,7 @@
         <v>0</v>
       </c>
       <c r="C396" s="27" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.35">
@@ -34281,7 +34288,7 @@
         <v>0</v>
       </c>
       <c r="C443" s="29" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.35">
@@ -34490,7 +34497,7 @@
         <v>5</v>
       </c>
       <c r="C462" s="29" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.35">
@@ -34897,7 +34904,7 @@
         <v>20</v>
       </c>
       <c r="C499" s="27" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.35">
@@ -34908,7 +34915,7 @@
         <v>0</v>
       </c>
       <c r="C500" s="29" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.35">
@@ -34974,7 +34981,7 @@
         <v>5</v>
       </c>
       <c r="C506" s="27" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.35">
@@ -35117,7 +35124,7 @@
         <v>1</v>
       </c>
       <c r="C519" s="29" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.35">
@@ -35524,7 +35531,7 @@
         <v>163</v>
       </c>
       <c r="C556" s="29" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.35">
@@ -35788,7 +35795,7 @@
         <v>0</v>
       </c>
       <c r="C580" s="27" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.35">
@@ -36074,7 +36081,7 @@
         <v>0</v>
       </c>
       <c r="C606" s="29" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.35">
@@ -36129,7 +36136,7 @@
         <v>0</v>
       </c>
       <c r="C611" s="27" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.35">
@@ -36140,7 +36147,7 @@
         <v>1</v>
       </c>
       <c r="C612" s="27" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.35">
@@ -36283,7 +36290,7 @@
         <v>261</v>
       </c>
       <c r="C625" s="29" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.35">
@@ -36382,7 +36389,7 @@
         <v>0</v>
       </c>
       <c r="C634" s="29" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.35">
@@ -36393,7 +36400,7 @@
         <v>0</v>
       </c>
       <c r="C635" s="29" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.35">
@@ -36404,7 +36411,7 @@
         <v>0</v>
       </c>
       <c r="C636" s="27" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.35">
@@ -36415,7 +36422,7 @@
         <v>0</v>
       </c>
       <c r="C637" s="29" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.35">
@@ -36470,7 +36477,7 @@
         <v>4013</v>
       </c>
       <c r="C642" s="29" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.35">
@@ -36481,7 +36488,7 @@
         <v>3163</v>
       </c>
       <c r="C643" s="27" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.35">
@@ -36492,7 +36499,7 @@
         <v>2377</v>
       </c>
       <c r="C644" s="29" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.35">
@@ -36525,7 +36532,7 @@
         <v>1</v>
       </c>
       <c r="C647" s="29" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.35">
@@ -36536,7 +36543,7 @@
         <v>14</v>
       </c>
       <c r="C648" s="27" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.35">
@@ -36547,7 +36554,7 @@
         <v>14</v>
       </c>
       <c r="C649" s="29" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.35">
@@ -36558,7 +36565,7 @@
         <v>5</v>
       </c>
       <c r="C650" s="27" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.35">
@@ -36569,7 +36576,7 @@
         <v>62</v>
       </c>
       <c r="C651" s="27" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.35">
@@ -36580,7 +36587,7 @@
         <v>717</v>
       </c>
       <c r="C652" s="29" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.35">
@@ -36591,7 +36598,7 @@
         <v>861</v>
       </c>
       <c r="C653" s="27" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.35">
@@ -36602,7 +36609,7 @@
         <v>60</v>
       </c>
       <c r="C654" s="29" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.35">
@@ -36668,7 +36675,7 @@
         <v>608</v>
       </c>
       <c r="C660" s="29" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.35">
@@ -36767,7 +36774,7 @@
         <v>1</v>
       </c>
       <c r="C669" s="29" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.35">
@@ -36866,7 +36873,7 @@
         <v>7</v>
       </c>
       <c r="C678" s="27" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.35">
@@ -36954,7 +36961,7 @@
         <v>0</v>
       </c>
       <c r="C686" s="29" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.35">
@@ -37020,7 +37027,7 @@
         <v>24</v>
       </c>
       <c r="C692" s="27" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.35">
@@ -37031,7 +37038,7 @@
         <v>2</v>
       </c>
       <c r="C693" s="29" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.35">
@@ -37042,7 +37049,7 @@
         <v>11</v>
       </c>
       <c r="C694" s="29" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.35">
@@ -37196,7 +37203,7 @@
         <v>0</v>
       </c>
       <c r="C708" s="29" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="709" spans="1:3" x14ac:dyDescent="0.35">
@@ -37306,7 +37313,7 @@
         <v>4</v>
       </c>
       <c r="C718" s="27" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="719" spans="1:3" x14ac:dyDescent="0.35">
@@ -37317,7 +37324,7 @@
         <v>18</v>
       </c>
       <c r="C719" s="29" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="720" spans="1:3" x14ac:dyDescent="0.35">
@@ -37328,7 +37335,7 @@
         <v>50</v>
       </c>
       <c r="C720" s="29" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="721" spans="1:3" x14ac:dyDescent="0.35">
@@ -37350,7 +37357,7 @@
         <v>3</v>
       </c>
       <c r="C722" s="29" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="723" spans="1:3" x14ac:dyDescent="0.35">
@@ -37570,7 +37577,7 @@
         <v>0</v>
       </c>
       <c r="C742" s="27" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="743" spans="1:3" x14ac:dyDescent="0.35">
@@ -37801,7 +37808,7 @@
         <v>0</v>
       </c>
       <c r="C763" s="27" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="764" spans="1:3" x14ac:dyDescent="0.35">
@@ -37889,7 +37896,7 @@
         <v>303</v>
       </c>
       <c r="C771" s="29" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.35">
@@ -37933,7 +37940,7 @@
         <v>133</v>
       </c>
       <c r="C775" s="29" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="776" spans="1:3" x14ac:dyDescent="0.35">
@@ -38219,7 +38226,7 @@
         <v>77</v>
       </c>
       <c r="C801" s="27" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="802" spans="1:3" x14ac:dyDescent="0.35">
@@ -38230,7 +38237,7 @@
         <v>114</v>
       </c>
       <c r="C802" s="29" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="803" spans="1:3" x14ac:dyDescent="0.35">
@@ -38252,7 +38259,7 @@
         <v>73</v>
       </c>
       <c r="C804" s="29" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.35">
@@ -38318,7 +38325,7 @@
         <v>58</v>
       </c>
       <c r="C810" s="29" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="811" spans="1:3" x14ac:dyDescent="0.35">
@@ -38329,7 +38336,7 @@
         <v>4</v>
       </c>
       <c r="C811" s="27" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="812" spans="1:3" x14ac:dyDescent="0.35">
@@ -38340,7 +38347,7 @@
         <v>60</v>
       </c>
       <c r="C812" s="29" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="813" spans="1:3" x14ac:dyDescent="0.35">
@@ -38439,7 +38446,7 @@
         <v>1</v>
       </c>
       <c r="C821" s="27" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="822" spans="1:3" x14ac:dyDescent="0.35">
@@ -38626,7 +38633,7 @@
         <v>1</v>
       </c>
       <c r="C838" s="27" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="839" spans="1:3" x14ac:dyDescent="0.35">
@@ -39099,7 +39106,7 @@
         <v>25</v>
       </c>
       <c r="C881" s="29" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.35">
@@ -39264,7 +39271,7 @@
         <v>0</v>
       </c>
       <c r="C896" s="29" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="897" spans="1:3" x14ac:dyDescent="0.35">
@@ -39286,7 +39293,7 @@
         <v>0</v>
       </c>
       <c r="C898" s="27" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="899" spans="1:3" x14ac:dyDescent="0.35">
@@ -39748,7 +39755,7 @@
         <v>0</v>
       </c>
       <c r="C940" s="29" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="941" spans="1:3" x14ac:dyDescent="0.35">
@@ -39770,7 +39777,7 @@
         <v>61</v>
       </c>
       <c r="C942" s="27" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="943" spans="1:3" x14ac:dyDescent="0.35">
@@ -39781,7 +39788,7 @@
         <v>49</v>
       </c>
       <c r="C943" s="29" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="944" spans="1:3" x14ac:dyDescent="0.35">
@@ -39792,7 +39799,7 @@
         <v>62</v>
       </c>
       <c r="C944" s="27" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="945" spans="1:3" x14ac:dyDescent="0.35">
@@ -39803,7 +39810,7 @@
         <v>67</v>
       </c>
       <c r="C945" s="29" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="946" spans="1:3" x14ac:dyDescent="0.35">
@@ -39814,7 +39821,7 @@
         <v>9</v>
       </c>
       <c r="C946" s="27" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="947" spans="1:3" x14ac:dyDescent="0.35">
@@ -39825,7 +39832,7 @@
         <v>31</v>
       </c>
       <c r="C947" s="29" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.35">
@@ -39836,7 +39843,7 @@
         <v>58</v>
       </c>
       <c r="C948" s="27" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="949" spans="1:3" x14ac:dyDescent="0.35">
@@ -39847,7 +39854,7 @@
         <v>57</v>
       </c>
       <c r="C949" s="29" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="950" spans="1:3" x14ac:dyDescent="0.35">
@@ -39858,7 +39865,7 @@
         <v>5</v>
       </c>
       <c r="C950" s="27" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="951" spans="1:3" x14ac:dyDescent="0.35">
@@ -39869,7 +39876,7 @@
         <v>53</v>
       </c>
       <c r="C951" s="29" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="952" spans="1:3" x14ac:dyDescent="0.35">
@@ -39880,7 +39887,7 @@
         <v>89</v>
       </c>
       <c r="C952" s="27" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="953" spans="1:3" x14ac:dyDescent="0.35">
@@ -39891,7 +39898,7 @@
         <v>60</v>
       </c>
       <c r="C953" s="27" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="954" spans="1:3" x14ac:dyDescent="0.35">
@@ -39902,7 +39909,7 @@
         <v>29</v>
       </c>
       <c r="C954" s="29" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="955" spans="1:3" x14ac:dyDescent="0.35">
@@ -39913,7 +39920,7 @@
         <v>79</v>
       </c>
       <c r="C955" s="27" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="956" spans="1:3" x14ac:dyDescent="0.35">
@@ -39924,7 +39931,7 @@
         <v>79</v>
       </c>
       <c r="C956" s="29" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="957" spans="1:3" x14ac:dyDescent="0.35">
@@ -39935,7 +39942,7 @@
         <v>67</v>
       </c>
       <c r="C957" s="27" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="958" spans="1:3" x14ac:dyDescent="0.35">
@@ -39946,7 +39953,7 @@
         <v>34</v>
       </c>
       <c r="C958" s="29" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.35">
@@ -39957,7 +39964,7 @@
         <v>25</v>
       </c>
       <c r="C959" s="27" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="960" spans="1:3" x14ac:dyDescent="0.35">
@@ -39968,7 +39975,7 @@
         <v>61</v>
       </c>
       <c r="C960" s="29" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="961" spans="1:3" x14ac:dyDescent="0.35">
@@ -39979,7 +39986,7 @@
         <v>61</v>
       </c>
       <c r="C961" s="27" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="962" spans="1:3" x14ac:dyDescent="0.35">
@@ -39990,7 +39997,7 @@
         <v>180</v>
       </c>
       <c r="C962" s="29" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="963" spans="1:3" x14ac:dyDescent="0.35">
@@ -40001,469 +40008,469 @@
         <v>180</v>
       </c>
       <c r="C963" s="29" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="964" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A964" s="26" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="B964" s="27">
         <v>0</v>
       </c>
       <c r="C964" s="27" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="965" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A965" s="28" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="B965" s="29">
         <v>49</v>
       </c>
       <c r="C965" s="29" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="966" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A966" s="26" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="B966" s="27">
         <v>0</v>
       </c>
       <c r="C966" s="27" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="967" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A967" s="28" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="B967" s="29">
         <v>0</v>
       </c>
       <c r="C967" s="29" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="968" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A968" s="26" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="B968" s="27">
         <v>0</v>
       </c>
       <c r="C968" s="27" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="969" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A969" s="28" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="B969" s="29">
         <v>0</v>
       </c>
       <c r="C969" s="29" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A970" s="26" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="B970" s="27">
         <v>17</v>
       </c>
       <c r="C970" s="27" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="971" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A971" s="28" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="B971" s="29">
         <v>0</v>
       </c>
       <c r="C971" s="29" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="972" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A972" s="26" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="B972" s="27">
         <v>1</v>
       </c>
       <c r="C972" s="27" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="973" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A973" s="28" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B973" s="29">
         <v>0</v>
       </c>
       <c r="C973" s="29" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="974" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A974" s="26" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="B974" s="27">
         <v>0</v>
       </c>
       <c r="C974" s="27" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="975" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A975" s="28" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="B975" s="29">
         <v>0</v>
       </c>
       <c r="C975" s="29" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="976" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A976" s="26" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="B976" s="27">
         <v>0</v>
       </c>
       <c r="C976" s="27" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="977" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A977" s="28" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="B977" s="29">
         <v>0</v>
       </c>
       <c r="C977" s="29" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="978" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A978" s="26" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="B978" s="27">
         <v>0</v>
       </c>
       <c r="C978" s="27" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="979" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A979" s="28" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="B979" s="29">
         <v>0</v>
       </c>
       <c r="C979" s="29" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="980" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A980" s="26" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="B980" s="27">
         <v>0</v>
       </c>
       <c r="C980" s="27" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A981" s="28" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="B981" s="29">
         <v>0</v>
       </c>
       <c r="C981" s="29" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="982" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A982" s="26" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="B982" s="27">
         <v>0</v>
       </c>
       <c r="C982" s="27" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="983" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A983" s="28" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="B983" s="29">
         <v>0</v>
       </c>
       <c r="C983" s="29" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="984" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A984" s="26" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="B984" s="27">
         <v>0</v>
       </c>
       <c r="C984" s="27" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="985" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A985" s="28" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="B985" s="29">
         <v>0</v>
       </c>
       <c r="C985" s="29" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="986" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A986" s="26" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="B986" s="27">
         <v>0</v>
       </c>
       <c r="C986" s="27" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="987" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A987" s="28" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="B987" s="29">
         <v>0</v>
       </c>
       <c r="C987" s="29" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="988" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A988" s="26" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="B988" s="27">
         <v>0</v>
       </c>
       <c r="C988" s="27" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="989" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A989" s="28" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="B989" s="29">
         <v>0</v>
       </c>
       <c r="C989" s="29" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="990" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A990" s="26" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="B990" s="27">
         <v>0</v>
       </c>
       <c r="C990" s="27" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="991" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A991" s="28" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="B991" s="29">
         <v>0</v>
       </c>
       <c r="C991" s="29" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A992" s="26" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="B992" s="27">
         <v>0</v>
       </c>
       <c r="C992" s="27" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="993" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A993" s="28" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="B993" s="29">
         <v>0</v>
       </c>
       <c r="C993" s="29" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="994" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A994" s="26" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="B994" s="27">
         <v>0</v>
       </c>
       <c r="C994" s="27" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="995" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A995" s="28" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="B995" s="29">
         <v>0</v>
       </c>
       <c r="C995" s="29" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="996" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A996" s="26" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="B996" s="27">
         <v>0</v>
       </c>
       <c r="C996" s="27" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="997" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A997" s="28" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="B997" s="29">
         <v>0</v>
       </c>
       <c r="C997" s="29" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="998" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A998" s="26" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="B998" s="27">
         <v>0</v>
       </c>
       <c r="C998" s="27" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="999" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A999" s="28" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="B999" s="29">
         <v>0</v>
       </c>
       <c r="C999" s="29" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="1000" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1000" s="26" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="B1000" s="27">
         <v>0</v>
       </c>
       <c r="C1000" s="27" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="1001" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1001" s="28" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="B1001" s="29">
         <v>0</v>
       </c>
       <c r="C1001" s="29" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="1002" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1002" s="26" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="B1002" s="27">
         <v>0</v>
       </c>
       <c r="C1002" s="27" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1003" s="28" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="B1003" s="29">
         <v>0</v>
       </c>
       <c r="C1003" s="29" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="1004" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1004" s="26" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="B1004" s="27">
         <v>0</v>
       </c>
       <c r="C1004" s="27" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="1005" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1005" s="28" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="B1005" s="29">
         <v>0</v>
       </c>
       <c r="C1005" s="29" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="1006" spans="1:3" x14ac:dyDescent="0.35">

--- a/posiciones_buscador.xlsx
+++ b/posiciones_buscador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\desarrollos\buscador_posiciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CC195A-8271-4AB5-81D5-10F4F6C9002B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE38C184-40C6-44FF-B134-6AF3BFB30B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81345FCE-0991-44B1-AB97-4BC767A118BC}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="1717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6157" uniqueCount="1717">
   <si>
     <t>Cod. De Barras</t>
   </si>
@@ -5481,8 +5481,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G1025" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G1025" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G1024" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G1024" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G967">
     <sortCondition ref="C1:C967"/>
   </sortState>
@@ -5818,7 +5818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD76C0E-5FFA-48DF-BC8E-37CFF7587C46}">
-  <dimension ref="A1:G1025"/>
+  <dimension ref="A1:G1024"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
@@ -28873,46 +28873,46 @@
       </c>
     </row>
     <row r="1003" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1003" s="20">
-        <v>7506452400038</v>
+      <c r="A1003" s="1">
+        <v>7502009749155</v>
       </c>
       <c r="B1003" s="12" t="s">
         <v>993</v>
       </c>
       <c r="C1003" s="16">
-        <v>9916</v>
+        <v>182</v>
       </c>
       <c r="D1003" s="16" t="s">
-        <v>910</v>
-      </c>
-      <c r="E1003" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1003" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1003" t="s">
-        <v>8</v>
+        <v>1696</v>
+      </c>
+      <c r="E1003" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1003" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1003" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="1004" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1004" s="1">
-        <v>7502009749155</v>
-      </c>
-      <c r="B1004" s="12" t="s">
-        <v>993</v>
+        <v>7503034275541</v>
+      </c>
+      <c r="B1004" s="7">
+        <v>7503034275541</v>
       </c>
       <c r="C1004" s="16">
-        <v>182</v>
+        <v>1137</v>
       </c>
       <c r="D1004" s="16" t="s">
-        <v>1696</v>
+        <v>1556</v>
       </c>
       <c r="E1004" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F1004" s="2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G1004" s="2" t="s">
         <v>10</v>
@@ -28920,16 +28920,16 @@
     </row>
     <row r="1005" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1005" s="1">
-        <v>7503034275541</v>
+        <v>7503034275558</v>
       </c>
       <c r="B1005" s="7">
-        <v>7503034275541</v>
+        <v>7503034275312</v>
       </c>
       <c r="C1005" s="16">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="D1005" s="16" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="E1005" s="2" t="s">
         <v>23</v>
@@ -28938,21 +28938,21 @@
         <v>24</v>
       </c>
       <c r="G1005" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1006" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1006" s="1">
-        <v>7503034275558</v>
+        <v>7503034275534</v>
       </c>
       <c r="B1006" s="7">
-        <v>7503034275312</v>
+        <v>7503034275305</v>
       </c>
       <c r="C1006" s="16">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D1006" s="16" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="E1006" s="2" t="s">
         <v>23</v>
@@ -28961,44 +28961,44 @@
         <v>24</v>
       </c>
       <c r="G1006" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1007" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1007" s="1">
-        <v>7503034275534</v>
-      </c>
-      <c r="B1007" s="7">
-        <v>7503034275305</v>
+        <v>7502247820913</v>
+      </c>
+      <c r="B1007" s="12" t="s">
+        <v>993</v>
       </c>
       <c r="C1007" s="16">
-        <v>1139</v>
+        <v>1153</v>
       </c>
       <c r="D1007" s="16" t="s">
-        <v>1558</v>
+        <v>1695</v>
       </c>
       <c r="E1007" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F1007" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G1007" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1008" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1008" s="1">
-        <v>7502247820913</v>
+        <v>7502275940218</v>
       </c>
       <c r="B1008" s="12" t="s">
         <v>993</v>
       </c>
       <c r="C1008" s="16">
-        <v>1153</v>
+        <v>9010</v>
       </c>
       <c r="D1008" s="16" t="s">
-        <v>1695</v>
+        <v>1578</v>
       </c>
       <c r="E1008" s="2" t="s">
         <v>23</v>
@@ -29007,21 +29007,21 @@
         <v>28</v>
       </c>
       <c r="G1008" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1009" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1009" s="1">
-        <v>7502275940218</v>
+        <v>7502275940355</v>
       </c>
       <c r="B1009" s="12" t="s">
         <v>993</v>
       </c>
       <c r="C1009" s="16">
-        <v>9010</v>
+        <v>9730</v>
       </c>
       <c r="D1009" s="16" t="s">
-        <v>1578</v>
+        <v>1597</v>
       </c>
       <c r="E1009" s="2" t="s">
         <v>23</v>
@@ -29030,27 +29030,27 @@
         <v>28</v>
       </c>
       <c r="G1009" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1010" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1010" s="1">
-        <v>7502275940355</v>
+        <v>7501438300326</v>
       </c>
       <c r="B1010" s="12" t="s">
         <v>993</v>
       </c>
       <c r="C1010" s="16">
-        <v>9730</v>
+        <v>99102</v>
       </c>
       <c r="D1010" s="16" t="s">
-        <v>1597</v>
+        <v>1699</v>
       </c>
       <c r="E1010" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F1010" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G1010" s="2" t="s">
         <v>9</v>
@@ -29058,16 +29058,16 @@
     </row>
     <row r="1011" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1011" s="1">
-        <v>7501438300326</v>
+        <v>7501438300548</v>
       </c>
       <c r="B1011" s="12" t="s">
         <v>993</v>
       </c>
       <c r="C1011" s="16">
-        <v>99102</v>
+        <v>99103</v>
       </c>
       <c r="D1011" s="16" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="E1011" s="2" t="s">
         <v>23</v>
@@ -29081,16 +29081,16 @@
     </row>
     <row r="1012" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1012" s="1">
-        <v>7501438300548</v>
+        <v>7502247820937</v>
       </c>
       <c r="B1012" s="12" t="s">
         <v>993</v>
       </c>
       <c r="C1012" s="16">
-        <v>99103</v>
+        <v>99104</v>
       </c>
       <c r="D1012" s="16" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="E1012" s="2" t="s">
         <v>23</v>
@@ -29104,16 +29104,16 @@
     </row>
     <row r="1013" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1013" s="1">
-        <v>7502247820937</v>
+        <v>7502247820869</v>
       </c>
       <c r="B1013" s="12" t="s">
         <v>993</v>
       </c>
       <c r="C1013" s="16">
-        <v>99104</v>
+        <v>99105</v>
       </c>
       <c r="D1013" s="16" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="E1013" s="2" t="s">
         <v>23</v>
@@ -29122,27 +29122,27 @@
         <v>24</v>
       </c>
       <c r="G1013" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1014" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1014" s="1">
-        <v>7502247820869</v>
+        <v>7506452400038</v>
       </c>
       <c r="B1014" s="12" t="s">
         <v>993</v>
       </c>
       <c r="C1014" s="16">
-        <v>99105</v>
+        <v>99106</v>
       </c>
       <c r="D1014" s="16" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="E1014" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F1014" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G1014" s="2" t="s">
         <v>8</v>
@@ -29150,16 +29150,16 @@
     </row>
     <row r="1015" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1015" s="1">
-        <v>7506452400038</v>
+        <v>7505023010874</v>
       </c>
       <c r="B1015" s="12" t="s">
         <v>993</v>
       </c>
       <c r="C1015" s="16">
-        <v>99106</v>
+        <v>99107</v>
       </c>
       <c r="D1015" s="16" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="E1015" s="2" t="s">
         <v>23</v>
@@ -29168,21 +29168,21 @@
         <v>28</v>
       </c>
       <c r="G1015" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1016" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1016" s="1">
-        <v>7505023010874</v>
+        <v>7505023011246</v>
       </c>
       <c r="B1016" s="12" t="s">
         <v>993</v>
       </c>
       <c r="C1016" s="16">
-        <v>99107</v>
+        <v>99108</v>
       </c>
       <c r="D1016" s="16" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="E1016" s="2" t="s">
         <v>23</v>
@@ -29191,220 +29191,197 @@
         <v>28</v>
       </c>
       <c r="G1016" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1017" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1017" s="1">
-        <v>7505023011246</v>
+        <v>7503036472771</v>
       </c>
       <c r="B1017" s="12" t="s">
         <v>993</v>
       </c>
       <c r="C1017" s="16">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D1017" s="16" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="E1017" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F1017" s="2" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="G1017" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1018" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1018" s="1">
-        <v>7503036472771</v>
+        <v>7503036472832</v>
       </c>
       <c r="B1018" s="12" t="s">
         <v>993</v>
       </c>
       <c r="C1018" s="16">
-        <v>99109</v>
+        <v>99110</v>
       </c>
       <c r="D1018" s="16" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="E1018" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F1018" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G1018" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1019" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1019" s="1">
-        <v>7503036472832</v>
-      </c>
-      <c r="B1019" s="12" t="s">
-        <v>993</v>
+        <v>7501349022515</v>
+      </c>
+      <c r="B1019" s="1" t="s">
+        <v>1712</v>
       </c>
       <c r="C1019" s="16">
-        <v>99110</v>
+        <v>158</v>
       </c>
       <c r="D1019" s="16" t="s">
-        <v>1707</v>
+        <v>1561</v>
       </c>
       <c r="E1019" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F1019" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G1019" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1020" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1020" s="1">
-        <v>7501349022515</v>
-      </c>
-      <c r="B1020" s="1" t="s">
-        <v>1712</v>
+        <v>7501349011625</v>
+      </c>
+      <c r="B1020" s="7">
+        <v>7501349029064</v>
       </c>
       <c r="C1020" s="16">
-        <v>158</v>
+        <v>705</v>
       </c>
       <c r="D1020" s="16" t="s">
-        <v>1561</v>
+        <v>1573</v>
       </c>
       <c r="E1020" s="2" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F1020" s="2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G1020" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1021" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1021" s="1">
-        <v>7501349011625</v>
-      </c>
-      <c r="B1021" s="7">
-        <v>7501349029064</v>
+        <v>7502211783275</v>
+      </c>
+      <c r="B1021" s="12" t="s">
+        <v>993</v>
       </c>
       <c r="C1021" s="16">
-        <v>705</v>
+        <v>1000</v>
       </c>
       <c r="D1021" s="16" t="s">
-        <v>1573</v>
-      </c>
-      <c r="E1021" s="2" t="s">
+        <v>1691</v>
+      </c>
+      <c r="E1021" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1021" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1021" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1022" s="20">
+        <v>7501349011984</v>
+      </c>
+      <c r="B1022" s="12" t="s">
+        <v>993</v>
+      </c>
+      <c r="C1022" s="16">
+        <v>714</v>
+      </c>
+      <c r="D1022" s="16" t="s">
+        <v>1575</v>
+      </c>
+      <c r="E1022" t="s">
         <v>31</v>
       </c>
-      <c r="F1021" s="2" t="s">
+      <c r="F1022" t="s">
         <v>6</v>
       </c>
-      <c r="G1021" s="2" t="s">
+      <c r="G1022" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="1022" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1022" s="1">
-        <v>7502211783275</v>
-      </c>
-      <c r="B1022" s="12" t="s">
-        <v>993</v>
-      </c>
-      <c r="C1022" s="16">
-        <v>1000</v>
-      </c>
-      <c r="D1022" s="16" t="s">
-        <v>1691</v>
-      </c>
-      <c r="E1022" t="s">
+    <row r="1023" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1023" s="1">
+        <v>7502009742736</v>
+      </c>
+      <c r="B1023" s="12" t="s">
+        <v>993</v>
+      </c>
+      <c r="C1023" s="16">
+        <v>99112</v>
+      </c>
+      <c r="D1023" s="16" t="s">
+        <v>1714</v>
+      </c>
+      <c r="E1023" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1023" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1023" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1024" s="20">
+        <v>7502006921967</v>
+      </c>
+      <c r="B1024" s="12" t="s">
+        <v>993</v>
+      </c>
+      <c r="C1024" s="22">
+        <v>1156</v>
+      </c>
+      <c r="D1024" s="16" t="s">
+        <v>1716</v>
+      </c>
+      <c r="E1024" t="s">
         <v>18</v>
       </c>
-      <c r="F1022" t="s">
+      <c r="F1024" t="s">
         <v>13</v>
       </c>
-      <c r="G1022" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="1023" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1023" s="20">
-        <v>7501349011984</v>
-      </c>
-      <c r="B1023" s="12" t="s">
-        <v>993</v>
-      </c>
-      <c r="C1023" s="16">
-        <v>714</v>
-      </c>
-      <c r="D1023" s="16" t="s">
-        <v>1575</v>
-      </c>
-      <c r="E1023" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1023" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1023" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="1024" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1024" s="1">
-        <v>7502009742736</v>
-      </c>
-      <c r="B1024" s="12" t="s">
-        <v>993</v>
-      </c>
-      <c r="C1024" s="16">
-        <v>99112</v>
-      </c>
-      <c r="D1024" s="16" t="s">
-        <v>1714</v>
-      </c>
-      <c r="E1024" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1024" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1024" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="1025" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1025" s="20">
-        <v>7502006921967</v>
-      </c>
-      <c r="B1025" s="12" t="s">
-        <v>993</v>
-      </c>
-      <c r="C1025" s="22">
-        <v>1156</v>
-      </c>
-      <c r="D1025" s="16" t="s">
-        <v>1716</v>
-      </c>
-      <c r="E1025" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1025" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1025" t="s">
+      <c r="G1024" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="D2:D652 D1002:D1003 D654:D934 D946 D935:D944 D947:D1001 D1025 D1004:D1024" calculatedColumn="1"/>
+    <ignoredError sqref="D2:D652 D1002 D654:D934 D946 D935:D944 D947:D1001 D1024 D1003:D1023" calculatedColumn="1"/>
     <ignoredError sqref="B949:B950" numberStoredAsText="1"/>
   </ignoredErrors>
   <tableParts count="1">

--- a/posiciones_buscador.xlsx
+++ b/posiciones_buscador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\desarrollos\buscador_posiciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757C684F-3A59-460E-A48C-92FD85C2B35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E35B7FC-A881-43E4-BA45-F89D5C6886AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81345FCE-0991-44B1-AB97-4BC767A118BC}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6172" uniqueCount="1721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6177" uniqueCount="1722">
   <si>
     <t>Cod. De Barras</t>
   </si>
@@ -5207,6 +5207,9 @@
   </si>
   <si>
     <t>CREATINE CLEAN 300GR. /60 PORCIONES</t>
+  </si>
+  <si>
+    <t>VITAMINA D3+K2 500MG. C/60 CAP.</t>
   </si>
 </sst>
 </file>
@@ -5493,8 +5496,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G1027" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G1027" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G1028" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G1028" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G967">
     <sortCondition ref="C1:C967"/>
   </sortState>
@@ -5830,7 +5833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD76C0E-5FFA-48DF-BC8E-37CFF7587C46}">
-  <dimension ref="A1:G1027"/>
+  <dimension ref="A1:G1028"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
@@ -29457,6 +29460,29 @@
       </c>
       <c r="G1027" t="s">
         <v>1719</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1028" s="1">
+        <v>7503058554059</v>
+      </c>
+      <c r="B1028" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="C1028" s="16">
+        <v>99113</v>
+      </c>
+      <c r="D1028" s="16" t="s">
+        <v>1721</v>
+      </c>
+      <c r="E1028" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1028" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1028" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/posiciones_buscador.xlsx
+++ b/posiciones_buscador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\desarrollos\buscador_posiciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E35B7FC-A881-43E4-BA45-F89D5C6886AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FFFB46A-5BE0-41F8-8778-80F97C127580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81345FCE-0991-44B1-AB97-4BC767A118BC}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6177" uniqueCount="1722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6177" uniqueCount="1721">
   <si>
     <t>Cod. De Barras</t>
   </si>
@@ -5201,9 +5201,6 @@
   </si>
   <si>
     <t>MAGNECIO CALMA500MG. C/60 CAP.</t>
-  </si>
-  <si>
-    <t>CA</t>
   </si>
   <si>
     <t>CREATINE CLEAN 300GR. /60 PORCIONES</t>
@@ -17867,7 +17864,7 @@
         <v>16</v>
       </c>
       <c r="G523" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.35">
@@ -27711,7 +27708,7 @@
         <v>6</v>
       </c>
       <c r="G951" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="952" spans="1:7" x14ac:dyDescent="0.35">
@@ -29446,11 +29443,11 @@
       <c r="B1027" s="12" t="s">
         <v>991</v>
       </c>
-      <c r="C1027" s="22">
+      <c r="C1027" s="16">
         <v>90116</v>
       </c>
       <c r="D1027" s="16" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="E1027" t="s">
         <v>21</v>
@@ -29459,7 +29456,7 @@
         <v>16</v>
       </c>
       <c r="G1027" t="s">
-        <v>1719</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1028" spans="1:7" x14ac:dyDescent="0.35">
@@ -29469,11 +29466,11 @@
       <c r="B1028" s="12" t="s">
         <v>991</v>
       </c>
-      <c r="C1028" s="16">
+      <c r="C1028" s="22">
         <v>99113</v>
       </c>
       <c r="D1028" s="16" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="E1028" t="s">
         <v>21</v>

--- a/posiciones_buscador.xlsx
+++ b/posiciones_buscador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\desarrollos\buscador_posiciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FFFB46A-5BE0-41F8-8778-80F97C127580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAEFACA5-5D45-42BE-900C-25F89235930E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81345FCE-0991-44B1-AB97-4BC767A118BC}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6177" uniqueCount="1721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6187" uniqueCount="1723">
   <si>
     <t>Cod. De Barras</t>
   </si>
@@ -5207,6 +5207,12 @@
   </si>
   <si>
     <t>VITAMINA D3+K2 500MG. C/60 CAP.</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 500 ML</t>
+  </si>
+  <si>
+    <t>CIANOCOBALAMINA 1000 MCG. C/30 TAB.</t>
   </si>
 </sst>
 </file>
@@ -5493,8 +5499,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G1028" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G1028" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}" name="Tabla13" displayName="Tabla13" ref="A1:G1030" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G1030" xr:uid="{C00A21B0-F40B-41CB-BB31-9BEA8E59BCFA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G967">
     <sortCondition ref="C1:C967"/>
   </sortState>
@@ -5830,7 +5836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD76C0E-5FFA-48DF-BC8E-37CFF7587C46}">
-  <dimension ref="A1:G1028"/>
+  <dimension ref="A1:G1030"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
@@ -29466,7 +29472,7 @@
       <c r="B1028" s="12" t="s">
         <v>991</v>
       </c>
-      <c r="C1028" s="22">
+      <c r="C1028" s="16">
         <v>99113</v>
       </c>
       <c r="D1028" s="16" t="s">
@@ -29479,13 +29485,59 @@
         <v>16</v>
       </c>
       <c r="G1028" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1029" s="1">
+        <v>7501590287992</v>
+      </c>
+      <c r="B1029" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="C1029" s="16">
+        <v>11340</v>
+      </c>
+      <c r="D1029" s="16" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E1029" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1029" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1029" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1030" s="20">
+        <v>7503031231007</v>
+      </c>
+      <c r="B1030" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="C1030" s="22">
+        <v>1154</v>
+      </c>
+      <c r="D1030" s="16" t="s">
+        <v>1721</v>
+      </c>
+      <c r="E1030" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1030" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1030" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="D2:D652 D1002 D654:D917 D946 D935:D944 D947:D1001 D1024:D1025 D1003:D1023 D918:D933 D1027" calculatedColumn="1"/>
+    <ignoredError sqref="D2:D652 D1002 D654:D917 D946 D935:D944 D947:D1001 D1024:D1025 D1003:D1023 D918:D933 D1027 D1029:D1030" calculatedColumn="1"/>
     <ignoredError sqref="B949:B950" numberStoredAsText="1"/>
   </ignoredErrors>
   <tableParts count="1">

--- a/posiciones_buscador.xlsx
+++ b/posiciones_buscador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\desarrollos\buscador_posiciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D35B88-649A-4F2C-8764-42B47E0C07B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4C1CFF-2668-4520-ABFB-54357304FAFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81345FCE-0991-44B1-AB97-4BC767A118BC}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6177" uniqueCount="1723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6180" uniqueCount="1723">
   <si>
     <t>Cod. De Barras</t>
   </si>
@@ -5355,7 +5355,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
@@ -5412,6 +5412,9 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5843,6 +5846,28 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="7">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{C250ABCF-3D9E-4F8C-BCD9-7F8E315ADBC3}">
+  <we:reference id="wa200010725" version="1.0.0.1" store="es-ES" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200010725" version="1.0.0.1" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;f0f9e0c3-86fa-4d24-abcf-f1482f884938&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD76C0E-5FFA-48DF-BC8E-37CFF7587C46}">
   <dimension ref="A1:G1028"/>
@@ -20853,7 +20878,7 @@
       <c r="A653" s="9">
         <v>7502007700479</v>
       </c>
-      <c r="B653" s="9" t="s">
+      <c r="B653" s="37" t="s">
         <v>990</v>
       </c>
       <c r="C653" s="34">
@@ -20876,7 +20901,7 @@
       <c r="A654" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B654" s="9" t="s">
+      <c r="B654" s="37" t="s">
         <v>990</v>
       </c>
       <c r="C654" s="5">
@@ -20899,7 +20924,7 @@
       <c r="A655" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B655" s="9" t="s">
+      <c r="B655" s="37" t="s">
         <v>990</v>
       </c>
       <c r="C655" s="5">
@@ -21083,8 +21108,8 @@
       <c r="A663" s="1">
         <v>7501563381153</v>
       </c>
-      <c r="B663" s="1" t="e">
-        <v>#N/A</v>
+      <c r="B663" s="1" t="s">
+        <v>990</v>
       </c>
       <c r="C663" s="2">
         <v>1140</v>
@@ -21106,8 +21131,8 @@
       <c r="A664" s="1">
         <v>7506624900113</v>
       </c>
-      <c r="B664" s="1" t="e">
-        <v>#N/A</v>
+      <c r="B664" s="1" t="s">
+        <v>990</v>
       </c>
       <c r="C664" s="2">
         <v>1141</v>
@@ -21129,8 +21154,8 @@
       <c r="A665" s="1">
         <v>6934520140899</v>
       </c>
-      <c r="B665" s="1" t="e">
-        <v>#N/A</v>
+      <c r="B665" s="1" t="s">
+        <v>990</v>
       </c>
       <c r="C665" s="2">
         <v>1142</v>
